--- a/Scout Selection.xlsx
+++ b/Scout Selection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djrre\OneDrive\Documents\Uni\Year 3\Maths and Data Modelling\Project 3 FPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE705F8-DC88-4DE3-9F24-05FF7773EFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84459217-9799-43EC-B157-58338578E4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{6BE00737-8581-4113-9953-3E2437BA74CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6BE00737-8581-4113-9953-3E2437BA74CB}"/>
   </bookViews>
   <sheets>
     <sheet name="21.22" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="298">
   <si>
     <t>Gameweek</t>
   </si>
@@ -585,6 +585,354 @@
   </si>
   <si>
     <t>Jarrad Branthwaite</t>
+  </si>
+  <si>
+    <t>Manuel Akanji</t>
+  </si>
+  <si>
+    <t>Sven Botman</t>
+  </si>
+  <si>
+    <t>Alphonse Areola</t>
+  </si>
+  <si>
+    <t>Ben White </t>
+  </si>
+  <si>
+    <t>Issa Kabore</t>
+  </si>
+  <si>
+    <t>Martin Odegaard</t>
+  </si>
+  <si>
+    <t>Carlton Morris</t>
+  </si>
+  <si>
+    <t>James Tarkowski</t>
+  </si>
+  <si>
+    <t>Thiago Silva</t>
+  </si>
+  <si>
+    <t>Pedro Neto</t>
+  </si>
+  <si>
+    <t>Rasmus Hojlund</t>
+  </si>
+  <si>
+    <t>Konstantinos Tsimikas</t>
+  </si>
+  <si>
+    <t>Diogo Dalot </t>
+  </si>
+  <si>
+    <t>Sam Johnstone</t>
+  </si>
+  <si>
+    <t>Matty Cash</t>
+  </si>
+  <si>
+    <t>Joachim Andersen</t>
+  </si>
+  <si>
+    <t>Evan Ferguson</t>
+  </si>
+  <si>
+    <t>Nayef Aguerd</t>
+  </si>
+  <si>
+    <t>Mohammed Kudus</t>
+  </si>
+  <si>
+    <t>Caoimhin Kelleher</t>
+  </si>
+  <si>
+    <t>Oleksandr Zinchenko</t>
+  </si>
+  <si>
+    <t>Hwang Hee-chan</t>
+  </si>
+  <si>
+    <t>Marcos Senesi</t>
+  </si>
+  <si>
+    <t>Neto </t>
+  </si>
+  <si>
+    <t>Richarlison </t>
+  </si>
+  <si>
+    <t>Nathan Ake</t>
+  </si>
+  <si>
+    <t>Alex Moreno</t>
+  </si>
+  <si>
+    <t>Michael Olise</t>
+  </si>
+  <si>
+    <t>Malo Gusto</t>
+  </si>
+  <si>
+    <t>Pascal Gross</t>
+  </si>
+  <si>
+    <t>Ederson </t>
+  </si>
+  <si>
+    <t>Kevin De Bruyne </t>
+  </si>
+  <si>
+    <t>Alfie Doughty</t>
+  </si>
+  <si>
+    <t>Virgil van Dijk </t>
+  </si>
+  <si>
+    <t>Jose Sa </t>
+  </si>
+  <si>
+    <t>Luis Diaz </t>
+  </si>
+  <si>
+    <t>Nathan Collins</t>
+  </si>
+  <si>
+    <t>Antonee Robinson </t>
+  </si>
+  <si>
+    <t>Conor Bradley</t>
+  </si>
+  <si>
+    <t>Kai Havertz</t>
+  </si>
+  <si>
+    <t>Stefan Ortega</t>
+  </si>
+  <si>
+    <t>Axel Disasi</t>
+  </si>
+  <si>
+    <t>Dean Henderson </t>
+  </si>
+  <si>
+    <t>Max Kilman</t>
+  </si>
+  <si>
+    <t>Djordje Petrovic</t>
+  </si>
+  <si>
+    <t>Fabian Schar</t>
+  </si>
+  <si>
+    <t>Harry Maguire</t>
+  </si>
+  <si>
+    <t>Cristian Romero</t>
+  </si>
+  <si>
+    <t>Hugo Lloris</t>
+  </si>
+  <si>
+    <t>Vitalii Mykolenko</t>
+  </si>
+  <si>
+    <t>James Ward-Prowse</t>
+  </si>
+  <si>
+    <t>Miguel Almiron</t>
+  </si>
+  <si>
+    <t>Aleksandar Mitrovic</t>
+  </si>
+  <si>
+    <t>Kurt Zouma</t>
+  </si>
+  <si>
+    <t>Bernardo </t>
+  </si>
+  <si>
+    <t>Wilfried Zaha</t>
+  </si>
+  <si>
+    <t>Callum Wilson</t>
+  </si>
+  <si>
+    <t>Jose Sa</t>
+  </si>
+  <si>
+    <t>Eric Dier</t>
+  </si>
+  <si>
+    <t>Timothy Castagne</t>
+  </si>
+  <si>
+    <t>Lukasz Fabianski </t>
+  </si>
+  <si>
+    <t>Andrew Robertson</t>
+  </si>
+  <si>
+    <t>Gianluca Scamacca</t>
+  </si>
+  <si>
+    <t>Ben White</t>
+  </si>
+  <si>
+    <t>Andreas Pereira</t>
+  </si>
+  <si>
+    <t>Anthony Martial</t>
+  </si>
+  <si>
+    <t>Wilfried Gnonto</t>
+  </si>
+  <si>
+    <t>Emerson Royal</t>
+  </si>
+  <si>
+    <t>Gavin Bazunu</t>
+  </si>
+  <si>
+    <t>Alexis Mac Allister</t>
+  </si>
+  <si>
+    <t>Jason Steele</t>
+  </si>
+  <si>
+    <t>David De Gea</t>
+  </si>
+  <si>
+    <t>Michael Keane</t>
+  </si>
+  <si>
+    <t>Solly March</t>
+  </si>
+  <si>
+    <t>Diogo Jota </t>
+  </si>
+  <si>
+    <t>Eberechi Eze </t>
+  </si>
+  <si>
+    <t>Jannik Vestergaard</t>
+  </si>
+  <si>
+    <t>Joshua King</t>
+  </si>
+  <si>
+    <t>Cesar Azpilicueta</t>
+  </si>
+  <si>
+    <t>Aymeric Laporte</t>
+  </si>
+  <si>
+    <t>Allan Saint-Maximin</t>
+  </si>
+  <si>
+    <t>Alex McCarthy</t>
+  </si>
+  <si>
+    <t>Andros Townsend</t>
+  </si>
+  <si>
+    <t>Aaron Cresswell</t>
+  </si>
+  <si>
+    <t>Marcal </t>
+  </si>
+  <si>
+    <t>Ethan Pinnock</t>
+  </si>
+  <si>
+    <t>Conor Gallagher</t>
+  </si>
+  <si>
+    <t>Adam Armstrong</t>
+  </si>
+  <si>
+    <t>Bernardo Silva</t>
+  </si>
+  <si>
+    <t>Antonio Rudiger</t>
+  </si>
+  <si>
+    <t>Maxwel Cornet</t>
+  </si>
+  <si>
+    <t>Neal Maupay</t>
+  </si>
+  <si>
+    <t>Jacob Ramsey</t>
+  </si>
+  <si>
+    <t>Armando Broja</t>
+  </si>
+  <si>
+    <t>Alvaro Fernandez</t>
+  </si>
+  <si>
+    <t>Vladimir Coufal</t>
+  </si>
+  <si>
+    <t>Demarai Gray</t>
+  </si>
+  <si>
+    <t>Kostas Tsimikas</t>
+  </si>
+  <si>
+    <t>Lucas Moura</t>
+  </si>
+  <si>
+    <t>Philippe Coutinho</t>
+  </si>
+  <si>
+    <t>Alexandre Lacazette</t>
+  </si>
+  <si>
+    <t>Patson Daka</t>
+  </si>
+  <si>
+    <t>Emiliano Buendia</t>
+  </si>
+  <si>
+    <t>Odsonne Edouard</t>
+  </si>
+  <si>
+    <t>Romain Saiss</t>
+  </si>
+  <si>
+    <t>Sadio Mane</t>
+  </si>
+  <si>
+    <t>Jan Bednarek</t>
+  </si>
+  <si>
+    <t>Joe Willock</t>
+  </si>
+  <si>
+    <t>Che Adams</t>
+  </si>
+  <si>
+    <t>Matt Doherty</t>
+  </si>
+  <si>
+    <t>Wout Weghorst</t>
+  </si>
+  <si>
+    <t>Kasper Schmeichel</t>
+  </si>
+  <si>
+    <t>Teemu Pukki</t>
+  </si>
+  <si>
+    <t>Fraser Forster</t>
+  </si>
+  <si>
+    <t>Jonny </t>
+  </si>
+  <si>
+    <t>Marcos Alonso</t>
   </si>
 </sst>
 </file>
@@ -962,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1967FA83-A894-45AF-9397-5DC671B5901D}">
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -979,7 +1327,7 @@
     <col min="22" max="22" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1050,12 +1398,16 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y2">
+        <f>SUM(C2:W2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1125,8 +1477,12 @@
       <c r="W3">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y3">
+        <f t="shared" ref="Y3:Y39" si="0">SUM(C3:W3)</f>
+        <v>83.499999999999986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1196,8 +1552,12 @@
       <c r="W4">
         <v>7.7</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y4">
+        <f t="shared" si="0"/>
+        <v>82.800000000000011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1267,8 +1627,12 @@
       <c r="W5">
         <v>7.9</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y5">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1338,170 +1702,2220 @@
       <c r="W6">
         <v>7.9</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>83.300000000000011</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7">
+        <v>4.5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>7.6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7">
+        <v>5.5</v>
+      </c>
+      <c r="H7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I7">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7">
+        <v>12.6</v>
+      </c>
+      <c r="L7" t="s">
+        <v>237</v>
+      </c>
+      <c r="M7">
+        <v>6.9</v>
+      </c>
+      <c r="N7" t="s">
+        <v>177</v>
+      </c>
+      <c r="O7">
+        <v>6.8</v>
+      </c>
+      <c r="P7" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q7">
+        <v>6.1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7">
+        <v>7.7</v>
+      </c>
+      <c r="T7" t="s">
+        <v>61</v>
+      </c>
+      <c r="U7">
+        <v>12.7</v>
+      </c>
+      <c r="V7" t="s">
+        <v>62</v>
+      </c>
+      <c r="W7">
+        <v>7.9</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="0"/>
+        <v>83.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8">
+        <v>4.5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>265</v>
+      </c>
+      <c r="E8">
+        <v>5.5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H8" t="s">
+        <v>266</v>
+      </c>
+      <c r="I8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8">
+        <v>12.6</v>
+      </c>
+      <c r="L8" t="s">
+        <v>76</v>
+      </c>
+      <c r="M8">
+        <v>6.5</v>
+      </c>
+      <c r="N8" t="s">
+        <v>60</v>
+      </c>
+      <c r="O8">
+        <v>6.3</v>
+      </c>
+      <c r="P8" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q8">
+        <v>6.2</v>
+      </c>
+      <c r="R8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8">
+        <v>12.7</v>
+      </c>
+      <c r="T8" t="s">
+        <v>87</v>
+      </c>
+      <c r="U8">
+        <v>11.7</v>
+      </c>
+      <c r="V8" t="s">
+        <v>62</v>
+      </c>
+      <c r="W8">
+        <v>8</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E9">
+        <v>6.1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>261</v>
+      </c>
+      <c r="G9">
+        <v>5.5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>150</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9">
+        <v>12.7</v>
+      </c>
+      <c r="L9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9">
+        <v>10.1</v>
+      </c>
+      <c r="N9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O9">
+        <v>7.9</v>
+      </c>
+      <c r="P9" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q9">
+        <v>6.3</v>
+      </c>
+      <c r="R9" t="s">
+        <v>145</v>
+      </c>
+      <c r="S9">
+        <v>10.5</v>
+      </c>
+      <c r="T9" t="s">
+        <v>62</v>
+      </c>
+      <c r="U9">
+        <v>8</v>
+      </c>
+      <c r="V9" t="s">
+        <v>262</v>
+      </c>
+      <c r="W9">
+        <v>6.8</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="0"/>
+        <v>83.499999999999986</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10">
+        <v>4.5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10">
+        <v>6.2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>261</v>
+      </c>
+      <c r="G10">
+        <v>5.5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10">
+        <v>5.3</v>
+      </c>
+      <c r="J10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10">
+        <v>12.8</v>
+      </c>
+      <c r="L10" t="s">
+        <v>67</v>
+      </c>
+      <c r="M10">
+        <v>10.1</v>
+      </c>
+      <c r="N10" t="s">
+        <v>221</v>
+      </c>
+      <c r="O10">
+        <v>8.1</v>
+      </c>
+      <c r="P10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q10">
+        <v>6.6</v>
+      </c>
+      <c r="R10" t="s">
+        <v>264</v>
+      </c>
+      <c r="S10">
+        <v>5.7</v>
+      </c>
+      <c r="T10" t="s">
+        <v>145</v>
+      </c>
+      <c r="U10">
+        <v>10.6</v>
+      </c>
+      <c r="V10" t="s">
+        <v>62</v>
+      </c>
+      <c r="W10">
+        <v>8.1</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="0"/>
+        <v>83.499999999999986</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11">
+        <v>7.6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11">
+        <v>6.4</v>
+      </c>
+      <c r="H11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11">
+        <v>5.8</v>
+      </c>
+      <c r="J11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11">
+        <v>12.9</v>
+      </c>
+      <c r="L11" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="N11" t="s">
+        <v>221</v>
+      </c>
+      <c r="O11">
+        <v>8.1</v>
+      </c>
+      <c r="P11" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q11">
+        <v>8.1</v>
+      </c>
+      <c r="R11" t="s">
+        <v>62</v>
+      </c>
+      <c r="S11">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="T11" t="s">
+        <v>203</v>
+      </c>
+      <c r="U11">
+        <v>5.7</v>
+      </c>
+      <c r="V11" t="s">
+        <v>259</v>
+      </c>
+      <c r="W11">
+        <v>5.6</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="0"/>
+        <v>83.600000000000009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12">
+        <v>4.7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>267</v>
+      </c>
+      <c r="I12">
+        <v>4.7</v>
+      </c>
+      <c r="J12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12">
+        <v>12.9</v>
+      </c>
+      <c r="L12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="N12" t="s">
+        <v>76</v>
+      </c>
+      <c r="O12">
+        <v>6.6</v>
+      </c>
+      <c r="P12" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q12">
+        <v>5.6</v>
+      </c>
+      <c r="R12" t="s">
+        <v>31</v>
+      </c>
+      <c r="S12">
+        <v>12.1</v>
+      </c>
+      <c r="T12" t="s">
+        <v>145</v>
+      </c>
+      <c r="U12">
+        <v>10.8</v>
+      </c>
+      <c r="V12" t="s">
+        <v>80</v>
+      </c>
+      <c r="W12">
+        <v>6.6</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="0"/>
+        <v>83.199999999999989</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13">
+        <v>7.7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13">
+        <v>6.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13">
+        <v>5.9</v>
+      </c>
+      <c r="J13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13">
+        <v>13</v>
+      </c>
+      <c r="L13" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="N13" t="s">
+        <v>53</v>
+      </c>
+      <c r="O13">
+        <v>6.3</v>
+      </c>
+      <c r="P13" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q13">
+        <v>5.9</v>
+      </c>
+      <c r="R13" t="s">
+        <v>31</v>
+      </c>
+      <c r="S13">
+        <v>12.2</v>
+      </c>
+      <c r="T13" t="s">
+        <v>238</v>
+      </c>
+      <c r="U13">
+        <v>7.4</v>
+      </c>
+      <c r="V13" t="s">
+        <v>269</v>
+      </c>
+      <c r="W13">
+        <v>5.9</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="0"/>
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14">
+        <v>4.8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14">
+        <v>7.8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14">
+        <v>6.6</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14">
+        <v>6.1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14">
+        <v>13</v>
+      </c>
+      <c r="L14" t="s">
+        <v>270</v>
+      </c>
+      <c r="M14">
+        <v>7.2</v>
+      </c>
+      <c r="N14" t="s">
+        <v>58</v>
+      </c>
+      <c r="O14">
+        <v>7.5</v>
+      </c>
+      <c r="P14" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q14">
+        <v>6</v>
+      </c>
+      <c r="R14" t="s">
+        <v>129</v>
+      </c>
+      <c r="S14">
+        <v>5.9</v>
+      </c>
+      <c r="T14" t="s">
+        <v>31</v>
+      </c>
+      <c r="U14">
+        <v>12.2</v>
+      </c>
+      <c r="V14" t="s">
+        <v>259</v>
+      </c>
+      <c r="W14">
+        <v>5.6</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="0"/>
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15">
+        <v>7.9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15">
+        <v>6.7</v>
+      </c>
+      <c r="H15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15">
+        <v>6.3</v>
+      </c>
+      <c r="J15" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="L15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15">
+        <v>13</v>
+      </c>
+      <c r="N15" t="s">
+        <v>67</v>
+      </c>
+      <c r="O15">
+        <v>10.4</v>
+      </c>
+      <c r="P15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q15">
+        <v>7.5</v>
+      </c>
+      <c r="R15" t="s">
+        <v>76</v>
+      </c>
+      <c r="S15">
+        <v>6.6</v>
+      </c>
+      <c r="T15" t="s">
+        <v>135</v>
+      </c>
+      <c r="U15">
+        <v>7.8</v>
+      </c>
+      <c r="V15" t="s">
+        <v>238</v>
+      </c>
+      <c r="W15">
+        <v>7.4</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="0"/>
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C16">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16">
+        <v>6.7</v>
+      </c>
+      <c r="H16" t="s">
+        <v>271</v>
+      </c>
+      <c r="I16">
+        <v>6</v>
+      </c>
+      <c r="J16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16">
+        <v>13</v>
+      </c>
+      <c r="L16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16">
+        <v>10.4</v>
+      </c>
+      <c r="N16" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16">
+        <v>8.1</v>
+      </c>
+      <c r="P16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q16">
+        <v>6.7</v>
+      </c>
+      <c r="R16" t="s">
+        <v>272</v>
+      </c>
+      <c r="S16">
+        <v>6.1</v>
+      </c>
+      <c r="T16" t="s">
+        <v>102</v>
+      </c>
+      <c r="U16">
+        <v>7.4</v>
+      </c>
+      <c r="V16" t="s">
+        <v>80</v>
+      </c>
+      <c r="W16">
+        <v>6.7</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="0"/>
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17">
+        <v>8.1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17">
+        <v>6.8</v>
+      </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17">
+        <v>6.2</v>
+      </c>
+      <c r="J17" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17">
+        <v>13.1</v>
+      </c>
+      <c r="L17" t="s">
+        <v>270</v>
+      </c>
+      <c r="M17">
+        <v>7.6</v>
+      </c>
+      <c r="N17" t="s">
+        <v>45</v>
+      </c>
+      <c r="O17">
+        <v>7.5</v>
+      </c>
+      <c r="P17" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q17">
+        <v>6.5</v>
+      </c>
+      <c r="R17" t="s">
+        <v>86</v>
+      </c>
+      <c r="S17">
+        <v>6.2</v>
+      </c>
+      <c r="T17" t="s">
+        <v>145</v>
+      </c>
+      <c r="U17">
+        <v>10.7</v>
+      </c>
+      <c r="V17" t="s">
+        <v>259</v>
+      </c>
+      <c r="W17">
+        <v>5.8</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" si="0"/>
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="Y18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="Y19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>253</v>
+      </c>
+      <c r="C20">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20">
+        <v>6.8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20">
+        <v>6.3</v>
+      </c>
+      <c r="H20" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20">
+        <v>5.2</v>
+      </c>
+      <c r="J20" t="s">
+        <v>67</v>
+      </c>
+      <c r="K20">
+        <v>10.3</v>
+      </c>
+      <c r="L20" t="s">
+        <v>75</v>
+      </c>
+      <c r="M20">
+        <v>8.6</v>
+      </c>
+      <c r="N20" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20">
+        <v>9.4</v>
+      </c>
+      <c r="P20" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q20">
+        <v>7.6</v>
+      </c>
+      <c r="R20" t="s">
+        <v>38</v>
+      </c>
+      <c r="S20">
+        <v>5.3</v>
+      </c>
+      <c r="T20" t="s">
+        <v>61</v>
+      </c>
+      <c r="U20">
+        <v>12.5</v>
+      </c>
+      <c r="V20" t="s">
+        <v>275</v>
+      </c>
+      <c r="W20">
+        <v>5.4</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="0"/>
+        <v>82.500000000000014</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>253</v>
+      </c>
+      <c r="C21">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21">
+        <v>6.9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21">
+        <v>6.4</v>
+      </c>
+      <c r="H21" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21">
+        <v>5.3</v>
+      </c>
+      <c r="J21" t="s">
+        <v>279</v>
+      </c>
+      <c r="K21">
+        <v>3.7</v>
+      </c>
+      <c r="L21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21">
+        <v>13</v>
+      </c>
+      <c r="N21" t="s">
+        <v>58</v>
+      </c>
+      <c r="O21">
+        <v>8.1</v>
+      </c>
+      <c r="P21" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q21">
+        <v>7.6</v>
+      </c>
+      <c r="R21" t="s">
+        <v>45</v>
+      </c>
+      <c r="S21">
+        <v>7.7</v>
+      </c>
+      <c r="T21" t="s">
+        <v>61</v>
+      </c>
+      <c r="U21">
+        <v>12.5</v>
+      </c>
+      <c r="V21" t="s">
+        <v>62</v>
+      </c>
+      <c r="W21">
+        <v>7.7</v>
+      </c>
+      <c r="Y21">
+        <f t="shared" si="0"/>
+        <v>84.000000000000014</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>276</v>
+      </c>
+      <c r="C22">
+        <v>4.5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22">
+        <v>5.3</v>
+      </c>
+      <c r="F22" t="s">
+        <v>254</v>
+      </c>
+      <c r="G22">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H22" t="s">
+        <v>277</v>
+      </c>
+      <c r="I22">
+        <v>4.7</v>
+      </c>
+      <c r="J22" t="s">
+        <v>82</v>
+      </c>
+      <c r="K22">
+        <v>11.9</v>
+      </c>
+      <c r="L22" t="s">
+        <v>67</v>
+      </c>
+      <c r="M22">
+        <v>10.5</v>
+      </c>
+      <c r="N22" t="s">
+        <v>53</v>
+      </c>
+      <c r="O22">
+        <v>6.6</v>
+      </c>
+      <c r="P22" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q22">
+        <v>5.5</v>
+      </c>
+      <c r="R22" t="s">
+        <v>31</v>
+      </c>
+      <c r="S22">
+        <v>12.2</v>
+      </c>
+      <c r="T22" t="s">
+        <v>62</v>
+      </c>
+      <c r="U22">
+        <v>7.8</v>
+      </c>
+      <c r="V22" t="s">
+        <v>80</v>
+      </c>
+      <c r="W22">
+        <v>6.6</v>
+      </c>
+      <c r="Y22">
+        <f t="shared" si="0"/>
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>253</v>
+      </c>
+      <c r="C23">
+        <v>5.2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23">
+        <v>8.4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G23">
+        <v>6.2</v>
+      </c>
+      <c r="H23" t="s">
+        <v>249</v>
+      </c>
+      <c r="I23">
+        <v>5</v>
+      </c>
+      <c r="J23" t="s">
+        <v>58</v>
+      </c>
+      <c r="K23">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="L23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M23">
+        <v>7.7</v>
+      </c>
+      <c r="N23" t="s">
+        <v>53</v>
+      </c>
+      <c r="O23">
+        <v>6.7</v>
+      </c>
+      <c r="P23" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q23">
+        <v>6.5</v>
+      </c>
+      <c r="R23" t="s">
+        <v>61</v>
+      </c>
+      <c r="S23">
+        <v>12.5</v>
+      </c>
+      <c r="T23" t="s">
+        <v>31</v>
+      </c>
+      <c r="U23">
+        <v>12.2</v>
+      </c>
+      <c r="V23" t="s">
+        <v>259</v>
+      </c>
+      <c r="W23">
+        <v>5.8</v>
+      </c>
+      <c r="Y23">
+        <f t="shared" si="0"/>
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>239</v>
+      </c>
+      <c r="C24">
+        <v>5.2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24">
+        <v>8.4</v>
+      </c>
+      <c r="F24" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24">
+        <v>7</v>
+      </c>
+      <c r="H24" t="s">
+        <v>57</v>
+      </c>
+      <c r="I24">
+        <v>5</v>
+      </c>
+      <c r="J24" t="s">
+        <v>82</v>
+      </c>
+      <c r="K24">
+        <v>12.1</v>
+      </c>
+      <c r="L24" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24">
+        <v>8.4</v>
+      </c>
+      <c r="N24" t="s">
+        <v>281</v>
+      </c>
+      <c r="O24">
+        <v>7</v>
+      </c>
+      <c r="P24" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q24">
+        <v>6.8</v>
+      </c>
+      <c r="R24" t="s">
+        <v>76</v>
+      </c>
+      <c r="S24">
+        <v>6.5</v>
+      </c>
+      <c r="T24" t="s">
+        <v>282</v>
+      </c>
+      <c r="U24">
+        <v>8.4</v>
+      </c>
+      <c r="V24" t="s">
+        <v>283</v>
+      </c>
+      <c r="W24">
+        <v>7.1</v>
+      </c>
+      <c r="Y24">
+        <f t="shared" si="0"/>
+        <v>81.900000000000006</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>253</v>
+      </c>
+      <c r="C25">
+        <v>5.2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25">
+        <v>8.5</v>
+      </c>
+      <c r="F25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25">
+        <v>7.1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>265</v>
+      </c>
+      <c r="I25">
+        <v>5.3</v>
+      </c>
+      <c r="J25" t="s">
+        <v>82</v>
+      </c>
+      <c r="K25">
+        <v>12.2</v>
+      </c>
+      <c r="L25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M25">
+        <v>10.6</v>
+      </c>
+      <c r="N25" t="s">
+        <v>58</v>
+      </c>
+      <c r="O25">
+        <v>8.4</v>
+      </c>
+      <c r="P25" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q25">
+        <v>6.9</v>
+      </c>
+      <c r="R25" t="s">
+        <v>284</v>
+      </c>
+      <c r="S25">
+        <v>6.2</v>
+      </c>
+      <c r="T25" t="s">
+        <v>285</v>
+      </c>
+      <c r="U25">
+        <v>6.5</v>
+      </c>
+      <c r="V25" t="s">
+        <v>109</v>
+      </c>
+      <c r="W25">
+        <v>6.7</v>
+      </c>
+      <c r="Y25">
+        <f t="shared" si="0"/>
+        <v>83.600000000000009</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>253</v>
+      </c>
+      <c r="C26">
+        <v>5.3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26">
+        <v>8.5</v>
+      </c>
+      <c r="F26" t="s">
+        <v>180</v>
+      </c>
+      <c r="G26">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H26" t="s">
+        <v>249</v>
+      </c>
+      <c r="I26">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J26" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26">
+        <v>12.8</v>
+      </c>
+      <c r="L26" t="s">
+        <v>66</v>
+      </c>
+      <c r="M26">
+        <v>11.7</v>
+      </c>
+      <c r="N26" t="s">
+        <v>53</v>
+      </c>
+      <c r="O26">
+        <v>6.9</v>
+      </c>
+      <c r="P26" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q26">
+        <v>5.4</v>
+      </c>
+      <c r="R26" t="s">
+        <v>274</v>
+      </c>
+      <c r="S26">
+        <v>4.7</v>
+      </c>
+      <c r="T26" t="s">
+        <v>61</v>
+      </c>
+      <c r="U26">
+        <v>12.5</v>
+      </c>
+      <c r="V26" t="s">
+        <v>273</v>
+      </c>
+      <c r="W26">
+        <v>6.5</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="0"/>
+        <v>84.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27">
+        <v>5.4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27">
+        <v>8.5</v>
+      </c>
+      <c r="F27" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27">
+        <v>5.3</v>
+      </c>
+      <c r="H27" t="s">
+        <v>286</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+      <c r="J27" t="s">
+        <v>27</v>
+      </c>
+      <c r="K27">
+        <v>13</v>
+      </c>
+      <c r="L27" t="s">
+        <v>287</v>
+      </c>
+      <c r="M27">
+        <v>11.7</v>
+      </c>
+      <c r="N27" t="s">
+        <v>237</v>
+      </c>
+      <c r="O27">
+        <v>6.8</v>
+      </c>
+      <c r="P27" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q27">
+        <v>6.4</v>
+      </c>
+      <c r="R27" t="s">
+        <v>272</v>
+      </c>
+      <c r="S27">
+        <v>5.9</v>
+      </c>
+      <c r="T27" t="s">
+        <v>282</v>
+      </c>
+      <c r="U27">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="V27" t="s">
+        <v>135</v>
+      </c>
+      <c r="W27">
+        <v>7.4</v>
+      </c>
+      <c r="Y27">
+        <f t="shared" si="0"/>
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="Y28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>239</v>
+      </c>
+      <c r="C29">
+        <v>5.3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>271</v>
+      </c>
+      <c r="E29">
+        <v>6.1</v>
+      </c>
+      <c r="F29" t="s">
+        <v>288</v>
+      </c>
+      <c r="G29">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="H29" t="s">
+        <v>227</v>
+      </c>
+      <c r="I29">
+        <v>4.3</v>
+      </c>
+      <c r="J29" t="s">
+        <v>27</v>
+      </c>
+      <c r="K29">
+        <v>13.2</v>
+      </c>
+      <c r="L29" t="s">
+        <v>45</v>
+      </c>
+      <c r="M29">
+        <v>7.5</v>
+      </c>
+      <c r="N29" t="s">
+        <v>281</v>
+      </c>
+      <c r="O29">
+        <v>7.4</v>
+      </c>
+      <c r="P29" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q29">
+        <v>5.7</v>
+      </c>
+      <c r="R29" t="s">
+        <v>31</v>
+      </c>
+      <c r="S29">
+        <v>12.3</v>
+      </c>
+      <c r="T29" t="s">
+        <v>135</v>
+      </c>
+      <c r="U29">
+        <v>7.5</v>
+      </c>
+      <c r="V29" t="s">
+        <v>290</v>
+      </c>
+      <c r="W29">
+        <v>7</v>
+      </c>
+      <c r="Y29">
+        <f t="shared" si="0"/>
+        <v>80.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30">
+        <v>8.5</v>
+      </c>
+      <c r="F30" t="s">
+        <v>261</v>
+      </c>
+      <c r="G30">
+        <v>5.8</v>
+      </c>
+      <c r="H30" t="s">
+        <v>291</v>
+      </c>
+      <c r="I30">
+        <v>4.7</v>
+      </c>
+      <c r="J30" t="s">
+        <v>227</v>
+      </c>
+      <c r="K30">
+        <v>4.3</v>
+      </c>
+      <c r="L30" t="s">
+        <v>27</v>
+      </c>
+      <c r="M30">
+        <v>13.2</v>
+      </c>
+      <c r="N30" t="s">
+        <v>67</v>
+      </c>
+      <c r="O30">
+        <v>10.8</v>
+      </c>
+      <c r="P30" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q30">
+        <v>6.5</v>
+      </c>
+      <c r="R30" t="s">
+        <v>154</v>
+      </c>
+      <c r="S30">
+        <v>4.5</v>
+      </c>
+      <c r="T30" t="s">
+        <v>31</v>
+      </c>
+      <c r="U30">
+        <v>12.3</v>
+      </c>
+      <c r="V30" t="s">
+        <v>282</v>
+      </c>
+      <c r="W30">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="Y30">
+        <f t="shared" si="0"/>
+        <v>83.999999999999986</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>239</v>
+      </c>
+      <c r="C31">
+        <v>5.3</v>
+      </c>
+      <c r="D31" t="s">
+        <v>196</v>
+      </c>
+      <c r="E31">
+        <v>5.2</v>
+      </c>
+      <c r="F31" t="s">
+        <v>286</v>
+      </c>
+      <c r="G31">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H31" t="s">
+        <v>291</v>
+      </c>
+      <c r="I31">
+        <v>4.8</v>
+      </c>
+      <c r="J31" t="s">
+        <v>67</v>
+      </c>
+      <c r="K31">
+        <v>10.9</v>
+      </c>
+      <c r="L31" t="s">
+        <v>281</v>
+      </c>
+      <c r="M31">
+        <v>7.5</v>
+      </c>
+      <c r="N31" t="s">
+        <v>44</v>
+      </c>
+      <c r="O31">
+        <v>6.7</v>
+      </c>
+      <c r="P31" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q31">
+        <v>6.7</v>
+      </c>
+      <c r="R31" t="s">
+        <v>31</v>
+      </c>
+      <c r="S31">
+        <v>12.4</v>
+      </c>
+      <c r="T31" t="s">
+        <v>282</v>
+      </c>
+      <c r="U31">
+        <v>8.4</v>
+      </c>
+      <c r="V31" t="s">
+        <v>80</v>
+      </c>
+      <c r="W31">
+        <v>6.6</v>
+      </c>
+      <c r="Y31">
+        <f t="shared" si="0"/>
+        <v>79.600000000000009</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32">
+        <v>5.4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>243</v>
+      </c>
+      <c r="E32">
+        <v>7.3</v>
+      </c>
+      <c r="F32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32">
+        <v>6.9</v>
+      </c>
+      <c r="H32" t="s">
+        <v>291</v>
+      </c>
+      <c r="I32">
+        <v>4.8</v>
+      </c>
+      <c r="J32" t="s">
+        <v>27</v>
+      </c>
+      <c r="K32">
+        <v>13.3</v>
+      </c>
+      <c r="L32" t="s">
+        <v>37</v>
+      </c>
+      <c r="M32">
+        <v>7.8</v>
+      </c>
+      <c r="N32" t="s">
+        <v>86</v>
+      </c>
+      <c r="O32">
+        <v>6.7</v>
+      </c>
+      <c r="P32" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q32">
+        <v>6.6</v>
+      </c>
+      <c r="R32" t="s">
+        <v>278</v>
+      </c>
+      <c r="S32">
+        <v>5.5</v>
+      </c>
+      <c r="T32" t="s">
+        <v>31</v>
+      </c>
+      <c r="U32">
+        <v>12.5</v>
+      </c>
+      <c r="V32" t="s">
+        <v>292</v>
+      </c>
+      <c r="W32">
+        <v>5.5</v>
+      </c>
+      <c r="Y32">
+        <f t="shared" si="0"/>
+        <v>82.300000000000011</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D33" t="s">
+        <v>271</v>
+      </c>
+      <c r="E33">
+        <v>6.1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>291</v>
+      </c>
+      <c r="G33">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H33" t="s">
+        <v>227</v>
+      </c>
+      <c r="I33">
+        <v>4.3</v>
+      </c>
+      <c r="J33" t="s">
+        <v>27</v>
+      </c>
+      <c r="K33">
+        <v>13.3</v>
+      </c>
+      <c r="L33" t="s">
+        <v>67</v>
+      </c>
+      <c r="M33">
+        <v>10.9</v>
+      </c>
+      <c r="N33" t="s">
+        <v>44</v>
+      </c>
+      <c r="O33">
+        <v>6.8</v>
+      </c>
+      <c r="P33" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q33">
+        <v>6.8</v>
+      </c>
+      <c r="R33" t="s">
+        <v>53</v>
+      </c>
+      <c r="S33">
+        <v>6.8</v>
+      </c>
+      <c r="T33" t="s">
+        <v>31</v>
+      </c>
+      <c r="U33">
+        <v>12.5</v>
+      </c>
+      <c r="V33" t="s">
+        <v>156</v>
+      </c>
+      <c r="W33">
+        <v>5.2</v>
+      </c>
+      <c r="Y33">
+        <f t="shared" si="0"/>
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>293</v>
+      </c>
+      <c r="C34">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D34" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>90</v>
+      </c>
+      <c r="G34">
+        <v>5.4</v>
+      </c>
+      <c r="H34" t="s">
+        <v>227</v>
+      </c>
+      <c r="I34">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J34" t="s">
+        <v>66</v>
+      </c>
+      <c r="K34">
+        <v>11.6</v>
+      </c>
+      <c r="L34" t="s">
+        <v>67</v>
+      </c>
+      <c r="M34">
+        <v>11.1</v>
+      </c>
+      <c r="N34" t="s">
+        <v>44</v>
+      </c>
+      <c r="O34">
+        <v>7</v>
+      </c>
+      <c r="P34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q34">
+        <v>6.8</v>
+      </c>
+      <c r="R34" t="s">
+        <v>232</v>
+      </c>
+      <c r="S34">
+        <v>6.4</v>
+      </c>
+      <c r="T34" t="s">
+        <v>31</v>
+      </c>
+      <c r="U34">
+        <v>12.6</v>
+      </c>
+      <c r="V34" t="s">
+        <v>109</v>
+      </c>
+      <c r="W34">
+        <v>6.7</v>
+      </c>
+      <c r="Y34">
+        <f t="shared" si="0"/>
+        <v>83.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35">
+        <v>6.3</v>
+      </c>
+      <c r="F35" t="s">
+        <v>261</v>
+      </c>
+      <c r="G35">
+        <v>5.9</v>
+      </c>
+      <c r="H35" t="s">
+        <v>180</v>
+      </c>
+      <c r="I35">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J35" t="s">
+        <v>27</v>
+      </c>
+      <c r="K35">
+        <v>13.2</v>
+      </c>
+      <c r="L35" t="s">
+        <v>75</v>
+      </c>
+      <c r="M35">
+        <v>8.6</v>
+      </c>
+      <c r="N35" t="s">
+        <v>221</v>
+      </c>
+      <c r="O35">
+        <v>7.9</v>
+      </c>
+      <c r="P35" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q35">
+        <v>7.7</v>
+      </c>
+      <c r="R35" t="s">
+        <v>43</v>
+      </c>
+      <c r="S35">
+        <v>6.4</v>
+      </c>
+      <c r="T35" t="s">
+        <v>61</v>
+      </c>
+      <c r="U35">
+        <v>12.2</v>
+      </c>
+      <c r="V35" t="s">
+        <v>294</v>
+      </c>
+      <c r="W35">
+        <v>6</v>
+      </c>
+      <c r="Y35">
+        <f t="shared" si="0"/>
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>295</v>
+      </c>
+      <c r="C36">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D36" t="s">
+        <v>243</v>
+      </c>
+      <c r="E36">
+        <v>7.3</v>
+      </c>
+      <c r="F36" t="s">
+        <v>34</v>
+      </c>
+      <c r="G36">
+        <v>7.1</v>
+      </c>
+      <c r="H36" t="s">
+        <v>296</v>
+      </c>
+      <c r="I36">
+        <v>4.5</v>
+      </c>
+      <c r="J36" t="s">
+        <v>176</v>
+      </c>
+      <c r="K36">
+        <v>4.3</v>
+      </c>
+      <c r="L36" t="s">
+        <v>27</v>
+      </c>
+      <c r="M36">
+        <v>13.3</v>
+      </c>
+      <c r="N36" t="s">
+        <v>82</v>
+      </c>
+      <c r="O36">
+        <v>11.9</v>
+      </c>
+      <c r="P36" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q36">
+        <v>11</v>
+      </c>
+      <c r="R36" t="s">
+        <v>45</v>
+      </c>
+      <c r="S36">
+        <v>7.7</v>
+      </c>
+      <c r="T36" t="s">
+        <v>281</v>
+      </c>
+      <c r="U36">
+        <v>7</v>
+      </c>
+      <c r="V36" t="s">
+        <v>168</v>
+      </c>
+      <c r="W36">
+        <v>5.5</v>
+      </c>
+      <c r="Y36">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>293</v>
+      </c>
+      <c r="C37">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37">
+        <v>8.4</v>
+      </c>
+      <c r="F37" t="s">
+        <v>34</v>
+      </c>
+      <c r="G37">
+        <v>7.2</v>
+      </c>
+      <c r="H37" t="s">
+        <v>297</v>
+      </c>
+      <c r="I37">
+        <v>5.7</v>
+      </c>
+      <c r="J37" t="s">
+        <v>27</v>
+      </c>
+      <c r="K37">
+        <v>13.3</v>
+      </c>
+      <c r="L37" t="s">
+        <v>82</v>
+      </c>
+      <c r="M37">
+        <v>11.9</v>
+      </c>
+      <c r="N37" t="s">
+        <v>86</v>
+      </c>
+      <c r="O37">
+        <v>6.7</v>
+      </c>
+      <c r="P37" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q37">
+        <v>6.4</v>
+      </c>
+      <c r="R37" t="s">
+        <v>43</v>
+      </c>
+      <c r="S37">
+        <v>6.3</v>
+      </c>
+      <c r="T37" t="s">
+        <v>206</v>
+      </c>
+      <c r="U37">
+        <v>7.5</v>
+      </c>
+      <c r="V37" t="s">
+        <v>168</v>
+      </c>
+      <c r="W37">
+        <v>5.5</v>
+      </c>
+      <c r="Y37">
+        <f t="shared" si="0"/>
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38">
+        <v>4.8</v>
+      </c>
+      <c r="D38" t="s">
+        <v>243</v>
+      </c>
+      <c r="E38">
+        <v>7.3</v>
+      </c>
+      <c r="F38" t="s">
+        <v>196</v>
+      </c>
+      <c r="G38">
+        <v>5.3</v>
+      </c>
+      <c r="H38" t="s">
+        <v>197</v>
+      </c>
+      <c r="I38">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J38" t="s">
+        <v>82</v>
+      </c>
+      <c r="K38">
+        <v>12</v>
+      </c>
+      <c r="L38" t="s">
+        <v>67</v>
+      </c>
+      <c r="M38">
+        <v>11</v>
+      </c>
+      <c r="N38" t="s">
+        <v>118</v>
+      </c>
+      <c r="O38">
+        <v>8</v>
+      </c>
+      <c r="P38" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q38">
+        <v>6.9</v>
+      </c>
+      <c r="R38" t="s">
+        <v>145</v>
+      </c>
+      <c r="S38">
+        <v>10.3</v>
+      </c>
+      <c r="T38" t="s">
+        <v>206</v>
+      </c>
+      <c r="U38">
+        <v>7.6</v>
+      </c>
+      <c r="V38" t="s">
+        <v>168</v>
+      </c>
+      <c r="W38">
+        <v>5.6</v>
+      </c>
+      <c r="Y38">
+        <f t="shared" si="0"/>
+        <v>83.399999999999991</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
+      </c>
+      <c r="Y39">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1512,7 +3926,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6523D19C-AF7E-47F2-B7FC-038031819EDE}">
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -1529,7 +3943,7 @@
     <col min="22" max="22" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1600,7 +4014,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1670,8 +4084,12 @@
       <c r="W2">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y2">
+        <f>SUM(C2:W2)</f>
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1741,8 +4159,12 @@
       <c r="W3">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y3">
+        <f t="shared" ref="Y3:Y39" si="0">SUM(C3:W3)</f>
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1812,8 +4234,12 @@
       <c r="W4">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y4">
+        <f t="shared" si="0"/>
+        <v>82.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1883,8 +4309,12 @@
       <c r="W5">
         <v>7.2</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y5">
+        <f t="shared" si="0"/>
+        <v>82.800000000000011</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1954,170 +4384,2484 @@
       <c r="W6">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>83.200000000000017</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>7.5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7">
+        <v>7.1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>91</v>
+      </c>
+      <c r="I7">
+        <v>4.5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>105</v>
+      </c>
+      <c r="K7">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7">
+        <v>8</v>
+      </c>
+      <c r="P7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q7">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="R7" t="s">
+        <v>40</v>
+      </c>
+      <c r="S7">
+        <v>11.9</v>
+      </c>
+      <c r="T7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U7">
+        <v>8.9</v>
+      </c>
+      <c r="V7" t="s">
+        <v>32</v>
+      </c>
+      <c r="W7">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="0"/>
+        <v>83.40000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8">
+        <v>7.5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8">
+        <v>13</v>
+      </c>
+      <c r="L8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8">
+        <v>6.5</v>
+      </c>
+      <c r="N8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8">
+        <v>6.5</v>
+      </c>
+      <c r="P8" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q8">
+        <v>6.5</v>
+      </c>
+      <c r="R8" t="s">
+        <v>40</v>
+      </c>
+      <c r="S8">
+        <v>12</v>
+      </c>
+      <c r="T8" t="s">
+        <v>32</v>
+      </c>
+      <c r="U8">
+        <v>8.1</v>
+      </c>
+      <c r="V8" t="s">
+        <v>80</v>
+      </c>
+      <c r="W8">
+        <v>7.2</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9">
+        <v>5.5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9">
+        <v>5.3</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>7.1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>231</v>
+      </c>
+      <c r="I9">
+        <v>4.5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>82</v>
+      </c>
+      <c r="K9">
+        <v>12.2</v>
+      </c>
+      <c r="L9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9">
+        <v>6.5</v>
+      </c>
+      <c r="N9" t="s">
+        <v>232</v>
+      </c>
+      <c r="O9">
+        <v>6.5</v>
+      </c>
+      <c r="P9" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q9">
+        <v>5</v>
+      </c>
+      <c r="R9" t="s">
+        <v>40</v>
+      </c>
+      <c r="S9">
+        <v>12</v>
+      </c>
+      <c r="T9" t="s">
+        <v>31</v>
+      </c>
+      <c r="U9">
+        <v>11.4</v>
+      </c>
+      <c r="V9" t="s">
+        <v>234</v>
+      </c>
+      <c r="W9">
+        <v>6.9</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="0"/>
+        <v>82.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10">
+        <v>4.5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10">
+        <v>7.4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10">
+        <v>7.2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10">
+        <v>6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>235</v>
+      </c>
+      <c r="K10">
+        <v>4.5</v>
+      </c>
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10">
+        <v>12.9</v>
+      </c>
+      <c r="N10" t="s">
+        <v>44</v>
+      </c>
+      <c r="O10">
+        <v>8</v>
+      </c>
+      <c r="P10" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q10">
+        <v>7</v>
+      </c>
+      <c r="R10" t="s">
+        <v>38</v>
+      </c>
+      <c r="S10">
+        <v>6.6</v>
+      </c>
+      <c r="T10" t="s">
+        <v>40</v>
+      </c>
+      <c r="U10">
+        <v>12.1</v>
+      </c>
+      <c r="V10" t="s">
+        <v>80</v>
+      </c>
+      <c r="W10">
+        <v>7.3</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="0"/>
+        <v>83.499999999999986</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11">
+        <v>4.5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11">
+        <v>7.2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11">
+        <v>5.5</v>
+      </c>
+      <c r="J11" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11">
+        <v>8.1</v>
+      </c>
+      <c r="N11" t="s">
+        <v>53</v>
+      </c>
+      <c r="O11">
+        <v>8.1</v>
+      </c>
+      <c r="P11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q11">
+        <v>8.1</v>
+      </c>
+      <c r="R11" t="s">
+        <v>237</v>
+      </c>
+      <c r="S11">
+        <v>7.3</v>
+      </c>
+      <c r="T11" t="s">
+        <v>40</v>
+      </c>
+      <c r="U11">
+        <v>12.2</v>
+      </c>
+      <c r="V11" t="s">
+        <v>238</v>
+      </c>
+      <c r="W11">
+        <v>7.2</v>
+      </c>
+      <c r="Y11">
+        <f>SUM(C11:W11)</f>
+        <v>84.200000000000017</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E12">
+        <v>5.2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>180</v>
+      </c>
+      <c r="G12">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12">
+        <v>11.7</v>
+      </c>
+      <c r="L12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="N12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="P12" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q12">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="R12" t="s">
+        <v>237</v>
+      </c>
+      <c r="S12">
+        <v>7.4</v>
+      </c>
+      <c r="T12" t="s">
+        <v>40</v>
+      </c>
+      <c r="U12">
+        <v>12.2</v>
+      </c>
+      <c r="V12" t="s">
+        <v>80</v>
+      </c>
+      <c r="W12">
+        <v>7.3</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="0"/>
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13">
+        <v>4.5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13">
+        <v>5.7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>150</v>
+      </c>
+      <c r="G13">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H13" t="s">
+        <v>241</v>
+      </c>
+      <c r="I13">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13">
+        <v>12.7</v>
+      </c>
+      <c r="L13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13">
+        <v>7.7</v>
+      </c>
+      <c r="N13" t="s">
+        <v>237</v>
+      </c>
+      <c r="O13">
+        <v>7.5</v>
+      </c>
+      <c r="P13" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q13">
+        <v>6.9</v>
+      </c>
+      <c r="R13" t="s">
+        <v>161</v>
+      </c>
+      <c r="S13">
+        <v>6.9</v>
+      </c>
+      <c r="T13" t="s">
+        <v>31</v>
+      </c>
+      <c r="U13">
+        <v>11.4</v>
+      </c>
+      <c r="V13" t="s">
+        <v>234</v>
+      </c>
+      <c r="W13">
+        <v>6.7</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14">
+        <v>7.3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>243</v>
+      </c>
+      <c r="G14">
+        <v>6.7</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J14" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14">
+        <v>8.4</v>
+      </c>
+      <c r="L14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="N14" t="s">
+        <v>86</v>
+      </c>
+      <c r="O14">
+        <v>7.9</v>
+      </c>
+      <c r="P14" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q14">
+        <v>7.5</v>
+      </c>
+      <c r="R14" t="s">
+        <v>40</v>
+      </c>
+      <c r="S14">
+        <v>12.1</v>
+      </c>
+      <c r="T14" t="s">
+        <v>41</v>
+      </c>
+      <c r="U14">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="V14" t="s">
+        <v>244</v>
+      </c>
+      <c r="W14">
+        <v>6.8</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="0"/>
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15">
+        <v>5.8</v>
+      </c>
+      <c r="H15" t="s">
+        <v>136</v>
+      </c>
+      <c r="I15">
+        <v>4.7</v>
+      </c>
+      <c r="J15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15">
+        <v>12.8</v>
+      </c>
+      <c r="L15" t="s">
+        <v>86</v>
+      </c>
+      <c r="M15">
+        <v>8</v>
+      </c>
+      <c r="N15" t="s">
+        <v>237</v>
+      </c>
+      <c r="O15">
+        <v>7.6</v>
+      </c>
+      <c r="P15" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q15">
+        <v>6.6</v>
+      </c>
+      <c r="R15" t="s">
+        <v>40</v>
+      </c>
+      <c r="S15">
+        <v>12.2</v>
+      </c>
+      <c r="T15" t="s">
+        <v>80</v>
+      </c>
+      <c r="U15">
+        <v>7.5</v>
+      </c>
+      <c r="V15" t="s">
+        <v>234</v>
+      </c>
+      <c r="W15">
+        <v>6.8</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="0"/>
+        <v>81.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16">
+        <v>7.4</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16">
+        <v>5.9</v>
+      </c>
+      <c r="H16" t="s">
+        <v>136</v>
+      </c>
+      <c r="I16">
+        <v>4.8</v>
+      </c>
+      <c r="J16" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16">
+        <v>8.5</v>
+      </c>
+      <c r="L16" t="s">
+        <v>161</v>
+      </c>
+      <c r="M16">
+        <v>6.9</v>
+      </c>
+      <c r="N16" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16">
+        <v>6.7</v>
+      </c>
+      <c r="P16" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q16">
+        <v>6.3</v>
+      </c>
+      <c r="R16" t="s">
+        <v>40</v>
+      </c>
+      <c r="S16">
+        <v>12.1</v>
+      </c>
+      <c r="T16" t="s">
+        <v>31</v>
+      </c>
+      <c r="U16">
+        <v>11.6</v>
+      </c>
+      <c r="V16" t="s">
+        <v>238</v>
+      </c>
+      <c r="W16">
+        <v>7.5</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="0"/>
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17">
+        <v>4.5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17">
+        <v>7.4</v>
+      </c>
+      <c r="F17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H17" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17">
+        <v>4.5</v>
+      </c>
+      <c r="J17" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17">
+        <v>12.7</v>
+      </c>
+      <c r="L17" t="s">
+        <v>161</v>
+      </c>
+      <c r="M17">
+        <v>7.1</v>
+      </c>
+      <c r="N17" t="s">
+        <v>38</v>
+      </c>
+      <c r="O17">
+        <v>6.8</v>
+      </c>
+      <c r="P17" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q17">
+        <v>6.7</v>
+      </c>
+      <c r="R17" t="s">
+        <v>233</v>
+      </c>
+      <c r="S17">
+        <v>5.8</v>
+      </c>
+      <c r="T17" t="s">
+        <v>40</v>
+      </c>
+      <c r="U17">
+        <v>12.2</v>
+      </c>
+      <c r="V17" t="s">
+        <v>31</v>
+      </c>
+      <c r="W17">
+        <v>11.6</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" si="0"/>
+        <v>84.399999999999991</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18">
+        <v>7.4</v>
+      </c>
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18">
+        <v>5.8</v>
+      </c>
+      <c r="H18" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18">
+        <v>4.8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>237</v>
+      </c>
+      <c r="K18">
+        <v>7.5</v>
+      </c>
+      <c r="L18" t="s">
+        <v>161</v>
+      </c>
+      <c r="M18">
+        <v>7.1</v>
+      </c>
+      <c r="N18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O18">
+        <v>6.8</v>
+      </c>
+      <c r="P18" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q18">
+        <v>6.7</v>
+      </c>
+      <c r="R18" t="s">
+        <v>40</v>
+      </c>
+      <c r="S18">
+        <v>12.2</v>
+      </c>
+      <c r="T18" t="s">
+        <v>31</v>
+      </c>
+      <c r="U18">
+        <v>11.6</v>
+      </c>
+      <c r="V18" t="s">
+        <v>41</v>
+      </c>
+      <c r="W18">
+        <v>9</v>
+      </c>
+      <c r="Y18">
+        <f t="shared" si="0"/>
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19">
+        <v>4.5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19">
+        <v>5.9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19">
+        <v>4.8</v>
+      </c>
+      <c r="H19" t="s">
+        <v>245</v>
+      </c>
+      <c r="I19">
+        <v>4.7</v>
+      </c>
+      <c r="J19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19">
+        <v>12.8</v>
+      </c>
+      <c r="L19" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="N19" t="s">
+        <v>29</v>
+      </c>
+      <c r="O19">
+        <v>6.8</v>
+      </c>
+      <c r="P19" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q19">
+        <v>5.9</v>
+      </c>
+      <c r="R19" t="s">
+        <v>40</v>
+      </c>
+      <c r="S19">
+        <v>12.2</v>
+      </c>
+      <c r="T19" t="s">
+        <v>31</v>
+      </c>
+      <c r="U19">
+        <v>11.6</v>
+      </c>
+      <c r="V19" t="s">
+        <v>234</v>
+      </c>
+      <c r="W19">
+        <v>6.9</v>
+      </c>
+      <c r="Y19">
+        <f>SUM(C19:W19)</f>
+        <v>84.399999999999991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20">
+        <v>4.5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <v>7.2</v>
+      </c>
+      <c r="F20" t="s">
+        <v>180</v>
+      </c>
+      <c r="G20">
+        <v>5.2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J20" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20">
+        <v>12.9</v>
+      </c>
+      <c r="L20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M20">
+        <v>7.6</v>
+      </c>
+      <c r="N20" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20">
+        <v>6.9</v>
+      </c>
+      <c r="P20" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q20">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="R20" t="s">
+        <v>40</v>
+      </c>
+      <c r="S20">
+        <v>12.2</v>
+      </c>
+      <c r="T20" t="s">
+        <v>31</v>
+      </c>
+      <c r="U20">
+        <v>11.6</v>
+      </c>
+      <c r="V20" t="s">
+        <v>234</v>
+      </c>
+      <c r="W20">
+        <v>7.1</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="0"/>
+        <v>84.699999999999989</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>212</v>
+      </c>
+      <c r="C21">
+        <v>5.4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21">
+        <v>6</v>
+      </c>
+      <c r="F21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H21" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J21" t="s">
+        <v>82</v>
+      </c>
+      <c r="K21">
+        <v>12.5</v>
+      </c>
+      <c r="L21" t="s">
+        <v>237</v>
+      </c>
+      <c r="M21">
+        <v>7.3</v>
+      </c>
+      <c r="N21" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21">
+        <v>7</v>
+      </c>
+      <c r="P21" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q21">
+        <v>5.9</v>
+      </c>
+      <c r="R21" t="s">
+        <v>40</v>
+      </c>
+      <c r="S21">
+        <v>12.2</v>
+      </c>
+      <c r="T21" t="s">
+        <v>31</v>
+      </c>
+      <c r="U21">
+        <v>11.6</v>
+      </c>
+      <c r="V21" t="s">
+        <v>247</v>
+      </c>
+      <c r="W21">
+        <v>6.6</v>
+      </c>
+      <c r="Y21">
+        <f t="shared" si="0"/>
+        <v>84.199999999999989</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>212</v>
+      </c>
+      <c r="C22">
+        <v>5.4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22">
+        <v>4.5</v>
+      </c>
+      <c r="H22" t="s">
+        <v>78</v>
+      </c>
+      <c r="I22">
+        <v>4.7</v>
+      </c>
+      <c r="J22" t="s">
+        <v>82</v>
+      </c>
+      <c r="K22">
+        <v>12.5</v>
+      </c>
+      <c r="L22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M22">
+        <v>7.1</v>
+      </c>
+      <c r="N22" t="s">
+        <v>187</v>
+      </c>
+      <c r="O22">
+        <v>6.8</v>
+      </c>
+      <c r="P22" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q22">
+        <v>5</v>
+      </c>
+      <c r="R22" t="s">
+        <v>40</v>
+      </c>
+      <c r="S22">
+        <v>12.2</v>
+      </c>
+      <c r="T22" t="s">
+        <v>31</v>
+      </c>
+      <c r="U22">
+        <v>11.7</v>
+      </c>
+      <c r="V22" t="s">
+        <v>80</v>
+      </c>
+      <c r="W22">
+        <v>7.6</v>
+      </c>
+      <c r="Y22">
+        <f t="shared" si="0"/>
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23">
+        <v>4.5</v>
+      </c>
+      <c r="D23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23">
+        <v>6.1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23">
+        <v>5.3</v>
+      </c>
+      <c r="H23" t="s">
+        <v>78</v>
+      </c>
+      <c r="I23">
+        <v>4.8</v>
+      </c>
+      <c r="J23" t="s">
+        <v>66</v>
+      </c>
+      <c r="K23">
+        <v>9.9</v>
+      </c>
+      <c r="L23" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23">
+        <v>7.2</v>
+      </c>
+      <c r="N23" t="s">
+        <v>187</v>
+      </c>
+      <c r="O23">
+        <v>6.9</v>
+      </c>
+      <c r="P23" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q23">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="R23" t="s">
+        <v>40</v>
+      </c>
+      <c r="S23">
+        <v>12.2</v>
+      </c>
+      <c r="T23" t="s">
+        <v>80</v>
+      </c>
+      <c r="U23">
+        <v>7.7</v>
+      </c>
+      <c r="V23" t="s">
+        <v>248</v>
+      </c>
+      <c r="W23">
+        <v>5</v>
+      </c>
+      <c r="Y23">
+        <f t="shared" si="0"/>
+        <v>74.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24">
+        <v>5.4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24">
+        <v>6.1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24">
+        <v>5.3</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>5.2</v>
+      </c>
+      <c r="J24" t="s">
+        <v>86</v>
+      </c>
+      <c r="K24">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="L24" t="s">
+        <v>75</v>
+      </c>
+      <c r="M24">
+        <v>7.7</v>
+      </c>
+      <c r="N24" t="s">
+        <v>29</v>
+      </c>
+      <c r="O24">
+        <v>7.2</v>
+      </c>
+      <c r="P24" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q24">
+        <v>5.2</v>
+      </c>
+      <c r="R24" t="s">
+        <v>40</v>
+      </c>
+      <c r="S24">
+        <v>12.2</v>
+      </c>
+      <c r="T24" t="s">
+        <v>80</v>
+      </c>
+      <c r="U24">
+        <v>7.7</v>
+      </c>
+      <c r="V24" t="s">
+        <v>168</v>
+      </c>
+      <c r="W24">
+        <v>6.8</v>
+      </c>
+      <c r="Y24">
+        <f t="shared" si="0"/>
+        <v>77.100000000000009</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25">
+        <v>4.7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25">
+        <v>5.8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25">
+        <v>5.2</v>
+      </c>
+      <c r="H25" t="s">
+        <v>65</v>
+      </c>
+      <c r="I25">
+        <v>4.8</v>
+      </c>
+      <c r="J25" t="s">
+        <v>86</v>
+      </c>
+      <c r="K25">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="L25" t="s">
+        <v>75</v>
+      </c>
+      <c r="M25">
+        <v>7.8</v>
+      </c>
+      <c r="N25" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25">
+        <v>7.3</v>
+      </c>
+      <c r="P25" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q25">
+        <v>5.3</v>
+      </c>
+      <c r="R25" t="s">
+        <v>40</v>
+      </c>
+      <c r="S25">
+        <v>12.2</v>
+      </c>
+      <c r="T25" t="s">
+        <v>31</v>
+      </c>
+      <c r="U25">
+        <v>11.8</v>
+      </c>
+      <c r="V25" t="s">
+        <v>80</v>
+      </c>
+      <c r="W25">
+        <v>7.6</v>
+      </c>
+      <c r="Y25">
+        <f t="shared" si="0"/>
+        <v>80.799999999999983</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26">
+        <v>7.3</v>
+      </c>
+      <c r="F26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26">
+        <v>5.2</v>
+      </c>
+      <c r="H26" t="s">
+        <v>65</v>
+      </c>
+      <c r="I26">
+        <v>4.8</v>
+      </c>
+      <c r="J26" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26">
+        <v>12.7</v>
+      </c>
+      <c r="L26" t="s">
+        <v>86</v>
+      </c>
+      <c r="M26">
+        <v>8.4</v>
+      </c>
+      <c r="N26" t="s">
+        <v>53</v>
+      </c>
+      <c r="O26">
+        <v>8</v>
+      </c>
+      <c r="P26" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q26">
+        <v>7.8</v>
+      </c>
+      <c r="R26" t="s">
+        <v>178</v>
+      </c>
+      <c r="S26">
+        <v>5.4</v>
+      </c>
+      <c r="T26" t="s">
+        <v>40</v>
+      </c>
+      <c r="U26">
+        <v>12.2</v>
+      </c>
+      <c r="V26" t="s">
+        <v>168</v>
+      </c>
+      <c r="W26">
+        <v>6.8</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="0"/>
+        <v>82.999999999999986</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27">
+        <v>4.7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27">
+        <v>5.2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>78</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+      <c r="H27" t="s">
+        <v>249</v>
+      </c>
+      <c r="I27">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J27" t="s">
+        <v>86</v>
+      </c>
+      <c r="K27">
+        <v>8.5</v>
+      </c>
+      <c r="L27" t="s">
+        <v>75</v>
+      </c>
+      <c r="M27">
+        <v>7.8</v>
+      </c>
+      <c r="N27" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27">
+        <v>7.2</v>
+      </c>
+      <c r="P27" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q27">
+        <v>5.3</v>
+      </c>
+      <c r="R27" t="s">
+        <v>40</v>
+      </c>
+      <c r="S27">
+        <v>12.2</v>
+      </c>
+      <c r="T27" t="s">
+        <v>31</v>
+      </c>
+      <c r="U27">
+        <v>11.7</v>
+      </c>
+      <c r="V27" t="s">
+        <v>80</v>
+      </c>
+      <c r="W27">
+        <v>7.6</v>
+      </c>
+      <c r="Y27">
+        <f t="shared" si="0"/>
+        <v>80.099999999999994</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>250</v>
+      </c>
+      <c r="C28">
+        <v>4.5</v>
+      </c>
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28">
+        <v>6</v>
+      </c>
+      <c r="F28" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H28" t="s">
+        <v>91</v>
+      </c>
+      <c r="I28">
+        <v>4.8</v>
+      </c>
+      <c r="J28" t="s">
+        <v>27</v>
+      </c>
+      <c r="K28">
+        <v>12.8</v>
+      </c>
+      <c r="L28" t="s">
+        <v>29</v>
+      </c>
+      <c r="M28">
+        <v>7.4</v>
+      </c>
+      <c r="N28" t="s">
+        <v>98</v>
+      </c>
+      <c r="O28">
+        <v>5.5</v>
+      </c>
+      <c r="P28" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q28">
+        <v>5.4</v>
+      </c>
+      <c r="R28" t="s">
+        <v>40</v>
+      </c>
+      <c r="S28">
+        <v>12.2</v>
+      </c>
+      <c r="T28" t="s">
+        <v>31</v>
+      </c>
+      <c r="U28">
+        <v>11.7</v>
+      </c>
+      <c r="V28" t="s">
+        <v>80</v>
+      </c>
+      <c r="W28">
+        <v>7.8</v>
+      </c>
+      <c r="Y28">
+        <f t="shared" si="0"/>
+        <v>83.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29">
+        <v>6</v>
+      </c>
+      <c r="F29" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29">
+        <v>5.9</v>
+      </c>
+      <c r="H29" t="s">
+        <v>202</v>
+      </c>
+      <c r="I29">
+        <v>5.2</v>
+      </c>
+      <c r="J29" t="s">
+        <v>65</v>
+      </c>
+      <c r="K29">
+        <v>4.8</v>
+      </c>
+      <c r="L29" t="s">
+        <v>44</v>
+      </c>
+      <c r="M29">
+        <v>8.1</v>
+      </c>
+      <c r="N29" t="s">
+        <v>86</v>
+      </c>
+      <c r="O29">
+        <v>8.5</v>
+      </c>
+      <c r="P29" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q29">
+        <v>6.6</v>
+      </c>
+      <c r="R29" t="s">
+        <v>31</v>
+      </c>
+      <c r="S29">
+        <v>11.7</v>
+      </c>
+      <c r="T29" t="s">
+        <v>80</v>
+      </c>
+      <c r="U29">
+        <v>7.8</v>
+      </c>
+      <c r="V29" t="s">
+        <v>102</v>
+      </c>
+      <c r="W29">
+        <v>7.4</v>
+      </c>
+      <c r="Y29">
+        <f t="shared" si="0"/>
+        <v>76.900000000000006</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>252</v>
+      </c>
+      <c r="C30">
+        <v>3.9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30">
+        <v>6.1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30">
+        <v>5.2</v>
+      </c>
+      <c r="H30" t="s">
+        <v>48</v>
+      </c>
+      <c r="I30">
+        <v>6</v>
+      </c>
+      <c r="J30" t="s">
+        <v>66</v>
+      </c>
+      <c r="K30">
+        <v>9.6</v>
+      </c>
+      <c r="L30" t="s">
+        <v>44</v>
+      </c>
+      <c r="M30">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="N30" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30">
+        <v>7.3</v>
+      </c>
+      <c r="P30" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q30">
+        <v>5.5</v>
+      </c>
+      <c r="R30" t="s">
+        <v>251</v>
+      </c>
+      <c r="S30">
+        <v>5.5</v>
+      </c>
+      <c r="T30" t="s">
+        <v>40</v>
+      </c>
+      <c r="U30">
+        <v>12</v>
+      </c>
+      <c r="V30" t="s">
+        <v>102</v>
+      </c>
+      <c r="W30">
+        <v>7.5</v>
+      </c>
+      <c r="Y30">
+        <f t="shared" si="0"/>
+        <v>76.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31">
+        <v>6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31">
+        <v>5.4</v>
+      </c>
+      <c r="H31" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31">
+        <v>6.1</v>
+      </c>
+      <c r="J31" t="s">
+        <v>86</v>
+      </c>
+      <c r="K31">
+        <v>8.6</v>
+      </c>
+      <c r="L31" t="s">
+        <v>44</v>
+      </c>
+      <c r="M31">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="N31" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31">
+        <v>7.3</v>
+      </c>
+      <c r="P31" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q31">
+        <v>5.6</v>
+      </c>
+      <c r="R31" t="s">
+        <v>40</v>
+      </c>
+      <c r="S31">
+        <v>12</v>
+      </c>
+      <c r="T31" t="s">
+        <v>31</v>
+      </c>
+      <c r="U31">
+        <v>11.7</v>
+      </c>
+      <c r="V31" t="s">
+        <v>102</v>
+      </c>
+      <c r="W31">
+        <v>7.5</v>
+      </c>
+      <c r="Y31">
+        <f t="shared" si="0"/>
+        <v>83.399999999999991</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>253</v>
+      </c>
+      <c r="C32">
+        <v>5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32">
+        <v>7.3</v>
+      </c>
+      <c r="F32" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32">
+        <v>4.8</v>
+      </c>
+      <c r="H32" t="s">
+        <v>254</v>
+      </c>
+      <c r="I32">
+        <v>4.2</v>
+      </c>
+      <c r="J32" t="s">
+        <v>27</v>
+      </c>
+      <c r="K32">
+        <v>12.8</v>
+      </c>
+      <c r="L32" t="s">
+        <v>75</v>
+      </c>
+      <c r="M32">
+        <v>7.3</v>
+      </c>
+      <c r="N32" t="s">
+        <v>38</v>
+      </c>
+      <c r="O32">
+        <v>6.7</v>
+      </c>
+      <c r="P32" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q32">
+        <v>5.7</v>
+      </c>
+      <c r="R32" t="s">
+        <v>209</v>
+      </c>
+      <c r="S32">
+        <v>5.4</v>
+      </c>
+      <c r="T32" t="s">
+        <v>40</v>
+      </c>
+      <c r="U32">
+        <v>12.2</v>
+      </c>
+      <c r="V32" t="s">
+        <v>31</v>
+      </c>
+      <c r="W32">
+        <v>11.7</v>
+      </c>
+      <c r="Y32">
+        <f t="shared" si="0"/>
+        <v>83.100000000000009</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33">
+        <v>7.4</v>
+      </c>
+      <c r="F33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33">
+        <v>6.2</v>
+      </c>
+      <c r="H33" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33">
+        <v>5.3</v>
+      </c>
+      <c r="J33" t="s">
+        <v>27</v>
+      </c>
+      <c r="K33">
+        <v>12.8</v>
+      </c>
+      <c r="L33" t="s">
+        <v>158</v>
+      </c>
+      <c r="M33">
+        <v>7.6</v>
+      </c>
+      <c r="N33" t="s">
+        <v>38</v>
+      </c>
+      <c r="O33">
+        <v>6.9</v>
+      </c>
+      <c r="P33" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q33">
+        <v>5.5</v>
+      </c>
+      <c r="R33" t="s">
+        <v>32</v>
+      </c>
+      <c r="S33">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="T33" t="s">
+        <v>80</v>
+      </c>
+      <c r="U33">
+        <v>7.7</v>
+      </c>
+      <c r="V33" t="s">
+        <v>102</v>
+      </c>
+      <c r="W33">
+        <v>7.7</v>
+      </c>
+      <c r="Y33">
+        <f t="shared" si="0"/>
+        <v>79.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>239</v>
+      </c>
+      <c r="C34">
+        <v>5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34">
+        <v>7.5</v>
+      </c>
+      <c r="F34" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34">
+        <v>6.2</v>
+      </c>
+      <c r="H34" t="s">
+        <v>208</v>
+      </c>
+      <c r="I34">
+        <v>4.5</v>
+      </c>
+      <c r="J34" t="s">
+        <v>27</v>
+      </c>
+      <c r="K34">
+        <v>13</v>
+      </c>
+      <c r="L34" t="s">
+        <v>29</v>
+      </c>
+      <c r="M34">
+        <v>7.1</v>
+      </c>
+      <c r="N34" t="s">
+        <v>38</v>
+      </c>
+      <c r="O34">
+        <v>6.9</v>
+      </c>
+      <c r="P34" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q34">
+        <v>5.6</v>
+      </c>
+      <c r="R34" t="s">
+        <v>40</v>
+      </c>
+      <c r="S34">
+        <v>12.3</v>
+      </c>
+      <c r="T34" t="s">
+        <v>102</v>
+      </c>
+      <c r="U34">
+        <v>7.7</v>
+      </c>
+      <c r="V34" t="s">
+        <v>80</v>
+      </c>
+      <c r="W34">
+        <v>7.6</v>
+      </c>
+      <c r="Y34">
+        <f>SUM(C34:W34)</f>
+        <v>83.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>253</v>
+      </c>
+      <c r="C35">
+        <v>5</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35">
+        <v>7.5</v>
+      </c>
+      <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35">
+        <v>5.5</v>
+      </c>
+      <c r="H35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I35">
+        <v>4.8</v>
+      </c>
+      <c r="J35" t="s">
+        <v>27</v>
+      </c>
+      <c r="K35">
+        <v>13</v>
+      </c>
+      <c r="L35" t="s">
+        <v>68</v>
+      </c>
+      <c r="M35">
+        <v>7.6</v>
+      </c>
+      <c r="N35" t="s">
+        <v>29</v>
+      </c>
+      <c r="O35">
+        <v>7.1</v>
+      </c>
+      <c r="P35" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q35">
+        <v>5.6</v>
+      </c>
+      <c r="R35" t="s">
+        <v>255</v>
+      </c>
+      <c r="S35">
+        <v>5.3</v>
+      </c>
+      <c r="T35" t="s">
+        <v>40</v>
+      </c>
+      <c r="U35">
+        <v>12.3</v>
+      </c>
+      <c r="V35" t="s">
+        <v>256</v>
+      </c>
+      <c r="W35">
+        <v>8.9</v>
+      </c>
+      <c r="Y35">
+        <f>SUM(C35:W35)</f>
+        <v>82.600000000000009</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>212</v>
+      </c>
+      <c r="C36">
+        <v>5.4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36">
+        <v>7.6</v>
+      </c>
+      <c r="F36" t="s">
+        <v>65</v>
+      </c>
+      <c r="G36">
+        <v>4.8</v>
+      </c>
+      <c r="H36" t="s">
+        <v>91</v>
+      </c>
+      <c r="I36">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J36" t="s">
+        <v>27</v>
+      </c>
+      <c r="K36">
+        <v>13</v>
+      </c>
+      <c r="L36" t="s">
+        <v>67</v>
+      </c>
+      <c r="M36">
+        <v>11.5</v>
+      </c>
+      <c r="N36" t="s">
+        <v>29</v>
+      </c>
+      <c r="O36">
+        <v>7.2</v>
+      </c>
+      <c r="P36" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q36">
+        <v>5.6</v>
+      </c>
+      <c r="R36" t="s">
+        <v>40</v>
+      </c>
+      <c r="S36">
+        <v>12.4</v>
+      </c>
+      <c r="T36" t="s">
+        <v>55</v>
+      </c>
+      <c r="U36">
+        <v>6</v>
+      </c>
+      <c r="V36" t="s">
+        <v>124</v>
+      </c>
+      <c r="W36">
+        <v>5.6</v>
+      </c>
+      <c r="Y36">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>253</v>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+      <c r="D37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37">
+        <v>7.6</v>
+      </c>
+      <c r="F37" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37">
+        <v>6.1</v>
+      </c>
+      <c r="H37" t="s">
+        <v>91</v>
+      </c>
+      <c r="I37">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J37" t="s">
+        <v>27</v>
+      </c>
+      <c r="K37">
+        <v>13.1</v>
+      </c>
+      <c r="L37" t="s">
+        <v>75</v>
+      </c>
+      <c r="M37">
+        <v>7.3</v>
+      </c>
+      <c r="N37" t="s">
+        <v>98</v>
+      </c>
+      <c r="O37">
+        <v>5.6</v>
+      </c>
+      <c r="P37" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q37">
+        <v>5.5</v>
+      </c>
+      <c r="R37" t="s">
+        <v>40</v>
+      </c>
+      <c r="S37">
+        <v>12.4</v>
+      </c>
+      <c r="T37" t="s">
+        <v>238</v>
+      </c>
+      <c r="U37">
+        <v>7.1</v>
+      </c>
+      <c r="V37" t="s">
+        <v>139</v>
+      </c>
+      <c r="W37">
+        <v>7</v>
+      </c>
+      <c r="Y37">
+        <f t="shared" si="0"/>
+        <v>81.599999999999994</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>239</v>
+      </c>
+      <c r="C38">
+        <v>5</v>
+      </c>
+      <c r="D38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38">
+        <v>7.7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38">
+        <v>5.2</v>
+      </c>
+      <c r="H38" t="s">
+        <v>91</v>
+      </c>
+      <c r="I38">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J38" t="s">
+        <v>27</v>
+      </c>
+      <c r="K38">
+        <v>13.1</v>
+      </c>
+      <c r="L38" t="s">
+        <v>66</v>
+      </c>
+      <c r="M38">
+        <v>9.5</v>
+      </c>
+      <c r="N38" t="s">
+        <v>75</v>
+      </c>
+      <c r="O38">
+        <v>7.4</v>
+      </c>
+      <c r="P38" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q38">
+        <v>7.2</v>
+      </c>
+      <c r="R38" t="s">
+        <v>98</v>
+      </c>
+      <c r="S38">
+        <v>5.6</v>
+      </c>
+      <c r="T38" t="s">
+        <v>40</v>
+      </c>
+      <c r="U38">
+        <v>12.4</v>
+      </c>
+      <c r="V38" t="s">
+        <v>55</v>
+      </c>
+      <c r="W38">
+        <v>6.1</v>
+      </c>
+      <c r="Y38">
+        <f t="shared" si="0"/>
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>253</v>
+      </c>
+      <c r="C39">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39">
+        <v>7.8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>197</v>
+      </c>
+      <c r="G39">
+        <v>4.5</v>
+      </c>
+      <c r="H39" t="s">
+        <v>189</v>
+      </c>
+      <c r="I39">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J39" t="s">
+        <v>27</v>
+      </c>
+      <c r="K39">
+        <v>13.1</v>
+      </c>
+      <c r="L39" t="s">
+        <v>75</v>
+      </c>
+      <c r="M39">
+        <v>7.5</v>
+      </c>
+      <c r="N39" t="s">
+        <v>257</v>
+      </c>
+      <c r="O39">
+        <v>5.7</v>
+      </c>
+      <c r="P39" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q39">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="R39" t="s">
+        <v>40</v>
+      </c>
+      <c r="S39">
+        <v>12.4</v>
+      </c>
+      <c r="T39" t="s">
+        <v>31</v>
+      </c>
+      <c r="U39">
+        <v>11.4</v>
+      </c>
+      <c r="V39" t="s">
+        <v>55</v>
+      </c>
+      <c r="W39">
+        <v>6.1</v>
+      </c>
+      <c r="Y39">
+        <f t="shared" si="0"/>
+        <v>82.800000000000011</v>
       </c>
     </row>
   </sheetData>
@@ -2127,7 +6871,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2177F9E4-D044-4408-B3F2-34055E8639B0}">
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -2144,7 +6888,7 @@
     <col min="22" max="22" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2215,7 +6959,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2285,8 +7029,12 @@
       <c r="W2">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y2">
+        <f>SUM(C2:W2)</f>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2356,8 +7104,12 @@
       <c r="W3">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y3">
+        <f t="shared" ref="Y3:Y39" si="0">SUM(C3:W3)</f>
+        <v>83.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2427,8 +7179,12 @@
       <c r="W4">
         <v>6.6</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y4">
+        <f t="shared" si="0"/>
+        <v>79.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2498,8 +7254,12 @@
       <c r="W5">
         <v>6.6</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y5">
+        <f t="shared" si="0"/>
+        <v>81.699999999999989</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2569,170 +7329,2484 @@
       <c r="W6">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7">
+        <v>4.5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7">
+        <v>5.3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>182</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s">
+        <v>183</v>
+      </c>
+      <c r="I7">
+        <v>4.5</v>
+      </c>
+      <c r="J7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7">
+        <v>12.5</v>
+      </c>
+      <c r="L7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7">
+        <v>8.9</v>
+      </c>
+      <c r="N7" t="s">
+        <v>92</v>
+      </c>
+      <c r="O7">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="P7" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q7">
+        <v>6.9</v>
+      </c>
+      <c r="R7" t="s">
+        <v>54</v>
+      </c>
+      <c r="S7">
+        <v>6.3</v>
+      </c>
+      <c r="T7" t="s">
+        <v>40</v>
+      </c>
+      <c r="U7">
+        <v>14.1</v>
+      </c>
+      <c r="V7" t="s">
+        <v>55</v>
+      </c>
+      <c r="W7">
+        <v>6.9</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="0"/>
+        <v>83.600000000000009</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8">
+        <v>4.2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8">
+        <v>6.6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>185</v>
+      </c>
+      <c r="G8">
+        <v>5.5</v>
+      </c>
+      <c r="H8" t="s">
+        <v>186</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8">
+        <v>12.5</v>
+      </c>
+      <c r="L8" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="N8" t="s">
+        <v>187</v>
+      </c>
+      <c r="O8">
+        <v>8.5</v>
+      </c>
+      <c r="P8" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8">
+        <v>7.1</v>
+      </c>
+      <c r="R8" t="s">
+        <v>154</v>
+      </c>
+      <c r="S8">
+        <v>5.6</v>
+      </c>
+      <c r="T8" t="s">
+        <v>40</v>
+      </c>
+      <c r="U8">
+        <v>14.1</v>
+      </c>
+      <c r="V8" t="s">
+        <v>188</v>
+      </c>
+      <c r="W8">
+        <v>5.6</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>82.899999999999991</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>4.7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" t="s">
+        <v>189</v>
+      </c>
+      <c r="I9">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9">
+        <v>12.6</v>
+      </c>
+      <c r="L9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="N9" t="s">
+        <v>44</v>
+      </c>
+      <c r="O9">
+        <v>8</v>
+      </c>
+      <c r="P9" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q9">
+        <v>5.7</v>
+      </c>
+      <c r="R9" t="s">
+        <v>40</v>
+      </c>
+      <c r="S9">
+        <v>14.1</v>
+      </c>
+      <c r="T9" t="s">
+        <v>102</v>
+      </c>
+      <c r="U9">
+        <v>8</v>
+      </c>
+      <c r="V9" t="s">
+        <v>192</v>
+      </c>
+      <c r="W9">
+        <v>7.1</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="0"/>
+        <v>83.899999999999991</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10">
+        <v>6.9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H10" t="s">
+        <v>194</v>
+      </c>
+      <c r="I10">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J10" t="s">
+        <v>193</v>
+      </c>
+      <c r="K10">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M10">
+        <v>12.6</v>
+      </c>
+      <c r="N10" t="s">
+        <v>67</v>
+      </c>
+      <c r="O10">
+        <v>9.5</v>
+      </c>
+      <c r="P10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q10">
+        <v>8.4</v>
+      </c>
+      <c r="R10" t="s">
+        <v>191</v>
+      </c>
+      <c r="S10">
+        <v>5.7</v>
+      </c>
+      <c r="T10" t="s">
+        <v>40</v>
+      </c>
+      <c r="U10">
+        <v>14</v>
+      </c>
+      <c r="V10" t="s">
+        <v>102</v>
+      </c>
+      <c r="W10">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="0"/>
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11">
+        <v>4.2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>5.2</v>
+      </c>
+      <c r="H11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11">
+        <v>12.8</v>
+      </c>
+      <c r="L11" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11">
+        <v>9.5</v>
+      </c>
+      <c r="N11" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11">
+        <v>8.5</v>
+      </c>
+      <c r="P11" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q11">
+        <v>8.5</v>
+      </c>
+      <c r="R11" t="s">
+        <v>53</v>
+      </c>
+      <c r="S11">
+        <v>7.4</v>
+      </c>
+      <c r="T11" t="s">
+        <v>102</v>
+      </c>
+      <c r="U11">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="V11" t="s">
+        <v>55</v>
+      </c>
+      <c r="W11">
+        <v>7.1</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="0"/>
+        <v>83.199999999999989</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12">
+        <v>4.5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>196</v>
+      </c>
+      <c r="E12">
+        <v>5.2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G12">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12">
+        <v>4.5</v>
+      </c>
+      <c r="J12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K12">
+        <v>12.8</v>
+      </c>
+      <c r="L12" t="s">
+        <v>67</v>
+      </c>
+      <c r="M12">
+        <v>9.6</v>
+      </c>
+      <c r="N12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12">
+        <v>7.5</v>
+      </c>
+      <c r="P12" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q12">
+        <v>7.4</v>
+      </c>
+      <c r="R12" t="s">
+        <v>40</v>
+      </c>
+      <c r="S12">
+        <v>14</v>
+      </c>
+      <c r="T12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U12">
+        <v>7.5</v>
+      </c>
+      <c r="V12" t="s">
+        <v>70</v>
+      </c>
+      <c r="W12">
+        <v>5.8</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="0"/>
+        <v>83.399999999999991</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13">
+        <v>4.8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G13">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H13" t="s">
+        <v>193</v>
+      </c>
+      <c r="I13">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J13" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13">
+        <v>12.9</v>
+      </c>
+      <c r="L13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13">
+        <v>9.6</v>
+      </c>
+      <c r="N13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13">
+        <v>7.7</v>
+      </c>
+      <c r="P13" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q13">
+        <v>6.8</v>
+      </c>
+      <c r="R13" t="s">
+        <v>154</v>
+      </c>
+      <c r="S13">
+        <v>5.7</v>
+      </c>
+      <c r="T13" t="s">
+        <v>40</v>
+      </c>
+      <c r="U13">
+        <v>14</v>
+      </c>
+      <c r="V13" t="s">
+        <v>198</v>
+      </c>
+      <c r="W13">
+        <v>6</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="0"/>
+        <v>84.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C14">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14">
+        <v>4.8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>199</v>
+      </c>
+      <c r="G14">
+        <v>4.5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14">
+        <v>4.5</v>
+      </c>
+      <c r="J14" t="s">
+        <v>51</v>
+      </c>
+      <c r="K14">
+        <v>13</v>
+      </c>
+      <c r="L14" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="N14" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14">
+        <v>7.5</v>
+      </c>
+      <c r="P14" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q14">
+        <v>6.5</v>
+      </c>
+      <c r="R14" t="s">
+        <v>40</v>
+      </c>
+      <c r="S14">
+        <v>14</v>
+      </c>
+      <c r="T14" t="s">
+        <v>102</v>
+      </c>
+      <c r="U14">
+        <v>8.5</v>
+      </c>
+      <c r="V14" t="s">
+        <v>124</v>
+      </c>
+      <c r="W14">
+        <v>6.4</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15">
+        <v>3.9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>202</v>
+      </c>
+      <c r="G15">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H15" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15">
+        <v>4.8</v>
+      </c>
+      <c r="J15" t="s">
+        <v>51</v>
+      </c>
+      <c r="K15">
+        <v>13</v>
+      </c>
+      <c r="L15" t="s">
+        <v>92</v>
+      </c>
+      <c r="M15">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N15" t="s">
+        <v>97</v>
+      </c>
+      <c r="O15">
+        <v>7</v>
+      </c>
+      <c r="P15" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q15">
+        <v>5.9</v>
+      </c>
+      <c r="R15" t="s">
+        <v>106</v>
+      </c>
+      <c r="S15">
+        <v>5.3</v>
+      </c>
+      <c r="T15" t="s">
+        <v>40</v>
+      </c>
+      <c r="U15">
+        <v>14</v>
+      </c>
+      <c r="V15" t="s">
+        <v>102</v>
+      </c>
+      <c r="W15">
+        <v>8.5</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="0"/>
+        <v>83.299999999999983</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>175</v>
+      </c>
+      <c r="E16">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>174</v>
+      </c>
+      <c r="G16">
+        <v>5.5</v>
+      </c>
+      <c r="H16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16">
+        <v>4.5</v>
+      </c>
+      <c r="J16" t="s">
+        <v>51</v>
+      </c>
+      <c r="K16">
+        <v>13.1</v>
+      </c>
+      <c r="L16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16">
+        <v>9.6</v>
+      </c>
+      <c r="N16" t="s">
+        <v>187</v>
+      </c>
+      <c r="O16">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="P16" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q16">
+        <v>7.1</v>
+      </c>
+      <c r="R16" t="s">
+        <v>203</v>
+      </c>
+      <c r="S16">
+        <v>5.6</v>
+      </c>
+      <c r="T16" t="s">
+        <v>40</v>
+      </c>
+      <c r="U16">
+        <v>14</v>
+      </c>
+      <c r="V16" t="s">
+        <v>93</v>
+      </c>
+      <c r="W16">
+        <v>5.3</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17">
+        <v>4.8</v>
+      </c>
+      <c r="H17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17">
+        <v>4.5</v>
+      </c>
+      <c r="J17" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17">
+        <v>13.1</v>
+      </c>
+      <c r="L17" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17">
+        <v>7.6</v>
+      </c>
+      <c r="N17" t="s">
+        <v>203</v>
+      </c>
+      <c r="O17">
+        <v>5.7</v>
+      </c>
+      <c r="P17" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q17">
+        <v>5.4</v>
+      </c>
+      <c r="R17" t="s">
+        <v>40</v>
+      </c>
+      <c r="S17">
+        <v>14</v>
+      </c>
+      <c r="T17" t="s">
+        <v>102</v>
+      </c>
+      <c r="U17">
+        <v>8.4</v>
+      </c>
+      <c r="V17" t="s">
+        <v>32</v>
+      </c>
+      <c r="W17">
+        <v>7.9</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" si="0"/>
+        <v>84.000000000000014</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18">
+        <v>5.4</v>
+      </c>
+      <c r="H18" t="s">
+        <v>204</v>
+      </c>
+      <c r="I18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J18" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18">
+        <v>13.2</v>
+      </c>
+      <c r="L18" t="s">
+        <v>67</v>
+      </c>
+      <c r="M18">
+        <v>9.6</v>
+      </c>
+      <c r="N18" t="s">
+        <v>92</v>
+      </c>
+      <c r="O18">
+        <v>9</v>
+      </c>
+      <c r="P18" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q18">
+        <v>7.7</v>
+      </c>
+      <c r="R18" t="s">
+        <v>37</v>
+      </c>
+      <c r="S18">
+        <v>7.6</v>
+      </c>
+      <c r="T18" t="s">
+        <v>139</v>
+      </c>
+      <c r="U18">
+        <v>7.6</v>
+      </c>
+      <c r="V18" t="s">
+        <v>124</v>
+      </c>
+      <c r="W18">
+        <v>6.6</v>
+      </c>
+      <c r="Y18">
+        <f t="shared" si="0"/>
+        <v>83.399999999999991</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F19" t="s">
+        <v>175</v>
+      </c>
+      <c r="G19">
+        <v>6.9</v>
+      </c>
+      <c r="H19" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19">
+        <v>5.5</v>
+      </c>
+      <c r="J19" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19">
+        <v>13.2</v>
+      </c>
+      <c r="L19" t="s">
+        <v>67</v>
+      </c>
+      <c r="M19">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="N19" t="s">
+        <v>200</v>
+      </c>
+      <c r="O19">
+        <v>6.7</v>
+      </c>
+      <c r="P19" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q19">
+        <v>5.6</v>
+      </c>
+      <c r="R19" t="s">
+        <v>30</v>
+      </c>
+      <c r="S19">
+        <v>5.6</v>
+      </c>
+      <c r="T19" t="s">
+        <v>102</v>
+      </c>
+      <c r="U19">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="V19" t="s">
+        <v>124</v>
+      </c>
+      <c r="W19">
+        <v>6.8</v>
+      </c>
+      <c r="Y19">
+        <f t="shared" si="0"/>
+        <v>82.100000000000009</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>205</v>
+      </c>
+      <c r="C20">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="F20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G20">
+        <v>6.9</v>
+      </c>
+      <c r="H20" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20">
+        <v>5.5</v>
+      </c>
+      <c r="J20" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20">
+        <v>13.2</v>
+      </c>
+      <c r="L20" t="s">
+        <v>67</v>
+      </c>
+      <c r="M20">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="N20" t="s">
+        <v>92</v>
+      </c>
+      <c r="O20">
+        <v>9</v>
+      </c>
+      <c r="P20" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q20">
+        <v>6.7</v>
+      </c>
+      <c r="R20" t="s">
+        <v>154</v>
+      </c>
+      <c r="S20">
+        <v>6.2</v>
+      </c>
+      <c r="T20" t="s">
+        <v>124</v>
+      </c>
+      <c r="U20">
+        <v>6.9</v>
+      </c>
+      <c r="V20" t="s">
+        <v>55</v>
+      </c>
+      <c r="W20">
+        <v>6.8</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="0"/>
+        <v>83.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21">
+        <v>8.4</v>
+      </c>
+      <c r="F21" t="s">
+        <v>207</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21" t="s">
+        <v>208</v>
+      </c>
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21" t="s">
+        <v>51</v>
+      </c>
+      <c r="K21">
+        <v>13.3</v>
+      </c>
+      <c r="L21" t="s">
+        <v>67</v>
+      </c>
+      <c r="M21">
+        <v>9.9</v>
+      </c>
+      <c r="N21" t="s">
+        <v>187</v>
+      </c>
+      <c r="O21">
+        <v>8.4</v>
+      </c>
+      <c r="P21" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q21">
+        <v>7.6</v>
+      </c>
+      <c r="R21" t="s">
+        <v>209</v>
+      </c>
+      <c r="S21">
+        <v>5.8</v>
+      </c>
+      <c r="T21" t="s">
+        <v>102</v>
+      </c>
+      <c r="U21">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="V21" t="s">
+        <v>124</v>
+      </c>
+      <c r="W21">
+        <v>7</v>
+      </c>
+      <c r="Y21">
+        <f t="shared" si="0"/>
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22">
+        <v>5.8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22" t="s">
+        <v>210</v>
+      </c>
+      <c r="I22">
+        <v>4.2</v>
+      </c>
+      <c r="J22" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22">
+        <v>9</v>
+      </c>
+      <c r="L22" t="s">
+        <v>37</v>
+      </c>
+      <c r="M22">
+        <v>7.9</v>
+      </c>
+      <c r="N22" t="s">
+        <v>206</v>
+      </c>
+      <c r="O22">
+        <v>6.9</v>
+      </c>
+      <c r="P22" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q22">
+        <v>6.4</v>
+      </c>
+      <c r="R22" t="s">
+        <v>106</v>
+      </c>
+      <c r="S22">
+        <v>5.7</v>
+      </c>
+      <c r="T22" t="s">
+        <v>102</v>
+      </c>
+      <c r="U22">
+        <v>8.9</v>
+      </c>
+      <c r="V22" t="s">
+        <v>80</v>
+      </c>
+      <c r="W22">
+        <v>7.9</v>
+      </c>
+      <c r="Y22">
+        <f t="shared" si="0"/>
+        <v>72.600000000000009</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>212</v>
+      </c>
+      <c r="C23">
+        <v>5.5</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23">
+        <v>8.5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23">
+        <v>5.9</v>
+      </c>
+      <c r="H23" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J23" t="s">
+        <v>213</v>
+      </c>
+      <c r="K23">
+        <v>10.6</v>
+      </c>
+      <c r="L23" t="s">
+        <v>37</v>
+      </c>
+      <c r="M23">
+        <v>8</v>
+      </c>
+      <c r="N23" t="s">
+        <v>58</v>
+      </c>
+      <c r="O23">
+        <v>7.9</v>
+      </c>
+      <c r="P23" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q23">
+        <v>7</v>
+      </c>
+      <c r="R23" t="s">
+        <v>200</v>
+      </c>
+      <c r="S23">
+        <v>6.8</v>
+      </c>
+      <c r="T23" t="s">
+        <v>41</v>
+      </c>
+      <c r="U23">
+        <v>7.4</v>
+      </c>
+      <c r="V23" t="s">
+        <v>124</v>
+      </c>
+      <c r="W23">
+        <v>7.1</v>
+      </c>
+      <c r="Y23">
+        <f t="shared" si="0"/>
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24">
+        <v>4.8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24">
+        <v>8.5</v>
+      </c>
+      <c r="F24" t="s">
+        <v>175</v>
+      </c>
+      <c r="G24">
+        <v>6.7</v>
+      </c>
+      <c r="H24" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24">
+        <v>5.9</v>
+      </c>
+      <c r="J24" t="s">
+        <v>213</v>
+      </c>
+      <c r="K24">
+        <v>10.7</v>
+      </c>
+      <c r="L24" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24">
+        <v>8</v>
+      </c>
+      <c r="N24" t="s">
+        <v>206</v>
+      </c>
+      <c r="O24">
+        <v>7</v>
+      </c>
+      <c r="P24" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q24">
+        <v>6.1</v>
+      </c>
+      <c r="R24" t="s">
+        <v>106</v>
+      </c>
+      <c r="S24">
+        <v>5.8</v>
+      </c>
+      <c r="T24" t="s">
+        <v>40</v>
+      </c>
+      <c r="U24">
+        <v>14</v>
+      </c>
+      <c r="V24" t="s">
+        <v>124</v>
+      </c>
+      <c r="W24">
+        <v>7.1</v>
+      </c>
+      <c r="Y24">
+        <f t="shared" si="0"/>
+        <v>84.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>212</v>
+      </c>
+      <c r="C25">
+        <v>5.5</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25">
+        <v>8.5</v>
+      </c>
+      <c r="F25" t="s">
+        <v>175</v>
+      </c>
+      <c r="G25">
+        <v>6.8</v>
+      </c>
+      <c r="H25" t="s">
+        <v>214</v>
+      </c>
+      <c r="I25">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J25" t="s">
+        <v>58</v>
+      </c>
+      <c r="K25">
+        <v>8.1</v>
+      </c>
+      <c r="L25" t="s">
+        <v>37</v>
+      </c>
+      <c r="M25">
+        <v>7.9</v>
+      </c>
+      <c r="N25" t="s">
+        <v>44</v>
+      </c>
+      <c r="O25">
+        <v>7.9</v>
+      </c>
+      <c r="P25" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q25">
+        <v>7.2</v>
+      </c>
+      <c r="R25" t="s">
+        <v>106</v>
+      </c>
+      <c r="S25">
+        <v>5.9</v>
+      </c>
+      <c r="T25" t="s">
+        <v>40</v>
+      </c>
+      <c r="U25">
+        <v>14.2</v>
+      </c>
+      <c r="V25" t="s">
+        <v>80</v>
+      </c>
+      <c r="W25">
+        <v>8.1</v>
+      </c>
+      <c r="Y25">
+        <f t="shared" si="0"/>
+        <v>84.699999999999989</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26">
+        <v>4.5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>215</v>
+      </c>
+      <c r="E26">
+        <v>6.4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H26" t="s">
+        <v>214</v>
+      </c>
+      <c r="I26">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J26" t="s">
+        <v>213</v>
+      </c>
+      <c r="K26">
+        <v>10.8</v>
+      </c>
+      <c r="L26" t="s">
+        <v>58</v>
+      </c>
+      <c r="M26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26">
+        <v>8</v>
+      </c>
+      <c r="P26" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q26">
+        <v>6.1</v>
+      </c>
+      <c r="R26" t="s">
+        <v>40</v>
+      </c>
+      <c r="S26">
+        <v>14.4</v>
+      </c>
+      <c r="T26" t="s">
+        <v>80</v>
+      </c>
+      <c r="U26">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="V26" t="s">
+        <v>41</v>
+      </c>
+      <c r="W26">
+        <v>7.6</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>216</v>
+      </c>
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27">
+        <v>5.2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>208</v>
+      </c>
+      <c r="G27">
+        <v>5.2</v>
+      </c>
+      <c r="H27" t="s">
+        <v>194</v>
+      </c>
+      <c r="I27">
+        <v>5.2</v>
+      </c>
+      <c r="J27" t="s">
+        <v>92</v>
+      </c>
+      <c r="K27">
+        <v>9.1</v>
+      </c>
+      <c r="L27" t="s">
+        <v>66</v>
+      </c>
+      <c r="M27">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="N27" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27">
+        <v>8.1</v>
+      </c>
+      <c r="P27" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q27">
+        <v>5.5</v>
+      </c>
+      <c r="R27" t="s">
+        <v>40</v>
+      </c>
+      <c r="S27">
+        <v>14.4</v>
+      </c>
+      <c r="T27" t="s">
+        <v>102</v>
+      </c>
+      <c r="U27">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="V27" t="s">
+        <v>80</v>
+      </c>
+      <c r="W27">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="Y27">
+        <f t="shared" si="0"/>
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C28">
+        <v>3.7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28">
+        <v>6.9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28">
+        <v>5.3</v>
+      </c>
+      <c r="H28" t="s">
+        <v>204</v>
+      </c>
+      <c r="I28">
+        <v>4.5</v>
+      </c>
+      <c r="J28" t="s">
+        <v>67</v>
+      </c>
+      <c r="K28">
+        <v>9.6</v>
+      </c>
+      <c r="L28" t="s">
+        <v>92</v>
+      </c>
+      <c r="M28">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="N28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28">
+        <v>8.1</v>
+      </c>
+      <c r="P28" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q28">
+        <v>7.5</v>
+      </c>
+      <c r="R28" t="s">
+        <v>154</v>
+      </c>
+      <c r="S28">
+        <v>6.1</v>
+      </c>
+      <c r="T28" t="s">
+        <v>40</v>
+      </c>
+      <c r="U28">
+        <v>14.4</v>
+      </c>
+      <c r="V28" t="s">
+        <v>102</v>
+      </c>
+      <c r="W28">
+        <v>8.9</v>
+      </c>
+      <c r="Y28">
+        <f t="shared" si="0"/>
+        <v>84.200000000000017</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D29" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29">
+        <v>5.3</v>
+      </c>
+      <c r="F29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G29">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H29" t="s">
+        <v>214</v>
+      </c>
+      <c r="I29">
+        <v>4.7</v>
+      </c>
+      <c r="J29" t="s">
+        <v>67</v>
+      </c>
+      <c r="K29">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L29" t="s">
+        <v>92</v>
+      </c>
+      <c r="M29">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="N29" t="s">
+        <v>53</v>
+      </c>
+      <c r="O29">
+        <v>7.9</v>
+      </c>
+      <c r="P29" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q29">
+        <v>5.7</v>
+      </c>
+      <c r="R29" t="s">
+        <v>102</v>
+      </c>
+      <c r="S29">
+        <v>9</v>
+      </c>
+      <c r="T29" t="s">
+        <v>124</v>
+      </c>
+      <c r="U29">
+        <v>7.1</v>
+      </c>
+      <c r="V29" t="s">
+        <v>188</v>
+      </c>
+      <c r="W29">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Y29">
+        <f t="shared" si="0"/>
+        <v>73.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30">
+        <v>4.5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30">
+        <v>5.8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>214</v>
+      </c>
+      <c r="G30">
+        <v>4.7</v>
+      </c>
+      <c r="H30" t="s">
+        <v>218</v>
+      </c>
+      <c r="I30">
+        <v>4.5</v>
+      </c>
+      <c r="J30" t="s">
+        <v>67</v>
+      </c>
+      <c r="K30">
+        <v>9.9</v>
+      </c>
+      <c r="L30" t="s">
+        <v>44</v>
+      </c>
+      <c r="M30">
+        <v>8</v>
+      </c>
+      <c r="N30" t="s">
+        <v>53</v>
+      </c>
+      <c r="O30">
+        <v>8</v>
+      </c>
+      <c r="P30" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q30">
+        <v>6.8</v>
+      </c>
+      <c r="R30" t="s">
+        <v>102</v>
+      </c>
+      <c r="S30">
+        <v>9</v>
+      </c>
+      <c r="T30" t="s">
+        <v>80</v>
+      </c>
+      <c r="U30">
+        <v>8.1</v>
+      </c>
+      <c r="V30" t="s">
+        <v>188</v>
+      </c>
+      <c r="W30">
+        <v>5.2</v>
+      </c>
+      <c r="Y30">
+        <f t="shared" si="0"/>
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31">
+        <v>4.8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>215</v>
+      </c>
+      <c r="E31">
+        <v>6.5</v>
+      </c>
+      <c r="F31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31">
+        <v>5.8</v>
+      </c>
+      <c r="H31" t="s">
+        <v>210</v>
+      </c>
+      <c r="I31">
+        <v>4.2</v>
+      </c>
+      <c r="J31" t="s">
+        <v>51</v>
+      </c>
+      <c r="K31">
+        <v>13.1</v>
+      </c>
+      <c r="L31" t="s">
+        <v>67</v>
+      </c>
+      <c r="M31">
+        <v>10.1</v>
+      </c>
+      <c r="N31" t="s">
+        <v>217</v>
+      </c>
+      <c r="O31">
+        <v>7.5</v>
+      </c>
+      <c r="P31" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q31">
+        <v>6.9</v>
+      </c>
+      <c r="R31" t="s">
+        <v>106</v>
+      </c>
+      <c r="S31">
+        <v>5.8</v>
+      </c>
+      <c r="T31" t="s">
+        <v>102</v>
+      </c>
+      <c r="U31">
+        <v>9</v>
+      </c>
+      <c r="V31" t="s">
+        <v>112</v>
+      </c>
+      <c r="W31">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="Y31">
+        <f t="shared" si="0"/>
+        <v>78.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32">
+        <v>4.2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32">
+        <v>5.3</v>
+      </c>
+      <c r="F32" t="s">
+        <v>219</v>
+      </c>
+      <c r="G32">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H32" t="s">
+        <v>220</v>
+      </c>
+      <c r="I32">
+        <v>4.2</v>
+      </c>
+      <c r="J32" t="s">
+        <v>51</v>
+      </c>
+      <c r="K32">
+        <v>13.3</v>
+      </c>
+      <c r="L32" t="s">
+        <v>67</v>
+      </c>
+      <c r="M32">
+        <v>10.1</v>
+      </c>
+      <c r="N32" t="s">
+        <v>92</v>
+      </c>
+      <c r="O32">
+        <v>9</v>
+      </c>
+      <c r="P32" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q32">
+        <v>7.5</v>
+      </c>
+      <c r="R32" t="s">
+        <v>221</v>
+      </c>
+      <c r="S32">
+        <v>7.2</v>
+      </c>
+      <c r="T32" t="s">
+        <v>40</v>
+      </c>
+      <c r="U32">
+        <v>14.3</v>
+      </c>
+      <c r="V32" t="s">
+        <v>112</v>
+      </c>
+      <c r="W32">
+        <v>4.7</v>
+      </c>
+      <c r="Y32">
+        <f t="shared" si="0"/>
+        <v>84.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>222</v>
+      </c>
+      <c r="C33">
+        <v>3.7</v>
+      </c>
+      <c r="D33" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33">
+        <v>5.3</v>
+      </c>
+      <c r="F33" t="s">
+        <v>223</v>
+      </c>
+      <c r="G33">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="H33" t="s">
+        <v>189</v>
+      </c>
+      <c r="I33">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="J33" t="s">
+        <v>51</v>
+      </c>
+      <c r="K33">
+        <v>13.4</v>
+      </c>
+      <c r="L33" t="s">
+        <v>187</v>
+      </c>
+      <c r="M33">
+        <v>8.5</v>
+      </c>
+      <c r="N33" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="P33" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q33">
+        <v>7.9</v>
+      </c>
+      <c r="R33" t="s">
+        <v>106</v>
+      </c>
+      <c r="S33">
+        <v>6</v>
+      </c>
+      <c r="T33" t="s">
+        <v>40</v>
+      </c>
+      <c r="U33">
+        <v>14.3</v>
+      </c>
+      <c r="V33" t="s">
+        <v>139</v>
+      </c>
+      <c r="W33">
+        <v>7.8</v>
+      </c>
+      <c r="Y33">
+        <f t="shared" si="0"/>
+        <v>84.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D34" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34">
+        <v>5.4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>150</v>
+      </c>
+      <c r="G34">
+        <v>5.2</v>
+      </c>
+      <c r="H34" t="s">
+        <v>210</v>
+      </c>
+      <c r="I34">
+        <v>4.3</v>
+      </c>
+      <c r="J34" t="s">
+        <v>51</v>
+      </c>
+      <c r="K34">
+        <v>13.4</v>
+      </c>
+      <c r="L34" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34">
+        <v>7.6</v>
+      </c>
+      <c r="N34" t="s">
+        <v>221</v>
+      </c>
+      <c r="O34">
+        <v>7.3</v>
+      </c>
+      <c r="P34" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q34">
+        <v>6.1</v>
+      </c>
+      <c r="R34" t="s">
+        <v>40</v>
+      </c>
+      <c r="S34">
+        <v>14.3</v>
+      </c>
+      <c r="T34" t="s">
+        <v>80</v>
+      </c>
+      <c r="U34">
+        <v>8.1</v>
+      </c>
+      <c r="V34" t="s">
+        <v>139</v>
+      </c>
+      <c r="W34">
+        <v>7.9</v>
+      </c>
+      <c r="Y34">
+        <f t="shared" si="0"/>
+        <v>84.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>224</v>
+      </c>
+      <c r="C35">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D35" t="s">
+        <v>215</v>
+      </c>
+      <c r="E35">
+        <v>6.6</v>
+      </c>
+      <c r="F35" t="s">
+        <v>90</v>
+      </c>
+      <c r="G35">
+        <v>5.4</v>
+      </c>
+      <c r="H35" t="s">
+        <v>225</v>
+      </c>
+      <c r="I35">
+        <v>4.5</v>
+      </c>
+      <c r="J35" t="s">
+        <v>51</v>
+      </c>
+      <c r="K35">
+        <v>13.5</v>
+      </c>
+      <c r="L35" t="s">
+        <v>92</v>
+      </c>
+      <c r="M35">
+        <v>9</v>
+      </c>
+      <c r="N35" t="s">
+        <v>217</v>
+      </c>
+      <c r="O35">
+        <v>7.8</v>
+      </c>
+      <c r="P35" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q35">
+        <v>7.2</v>
+      </c>
+      <c r="R35" t="s">
+        <v>54</v>
+      </c>
+      <c r="S35">
+        <v>6</v>
+      </c>
+      <c r="T35" t="s">
+        <v>124</v>
+      </c>
+      <c r="U35">
+        <v>7.2</v>
+      </c>
+      <c r="V35" t="s">
+        <v>156</v>
+      </c>
+      <c r="W35">
+        <v>5</v>
+      </c>
+      <c r="Y35">
+        <f t="shared" si="0"/>
+        <v>76.600000000000009</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36">
+        <v>5.8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>227</v>
+      </c>
+      <c r="G36">
+        <v>5.7</v>
+      </c>
+      <c r="H36" t="s">
+        <v>228</v>
+      </c>
+      <c r="I36">
+        <v>4.2</v>
+      </c>
+      <c r="J36" t="s">
+        <v>67</v>
+      </c>
+      <c r="K36">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L36" t="s">
+        <v>66</v>
+      </c>
+      <c r="M36">
+        <v>8.4</v>
+      </c>
+      <c r="N36" t="s">
+        <v>106</v>
+      </c>
+      <c r="O36">
+        <v>6.2</v>
+      </c>
+      <c r="P36" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q36">
+        <v>5.8</v>
+      </c>
+      <c r="R36" t="s">
+        <v>139</v>
+      </c>
+      <c r="S36">
+        <v>7.8</v>
+      </c>
+      <c r="T36" t="s">
+        <v>99</v>
+      </c>
+      <c r="U36">
+        <v>6.8</v>
+      </c>
+      <c r="V36" t="s">
+        <v>156</v>
+      </c>
+      <c r="W36">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Y36">
+        <f t="shared" si="0"/>
+        <v>70.199999999999989</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37">
+        <v>4.7</v>
+      </c>
+      <c r="D37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37">
+        <v>8.4</v>
+      </c>
+      <c r="F37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G37">
+        <v>5.4</v>
+      </c>
+      <c r="H37" t="s">
+        <v>126</v>
+      </c>
+      <c r="I37">
+        <v>5</v>
+      </c>
+      <c r="J37" t="s">
+        <v>92</v>
+      </c>
+      <c r="K37">
+        <v>9</v>
+      </c>
+      <c r="L37" t="s">
+        <v>37</v>
+      </c>
+      <c r="M37">
+        <v>8.4</v>
+      </c>
+      <c r="N37" t="s">
+        <v>221</v>
+      </c>
+      <c r="O37">
+        <v>7.5</v>
+      </c>
+      <c r="P37" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q37">
+        <v>6.2</v>
+      </c>
+      <c r="R37" t="s">
+        <v>40</v>
+      </c>
+      <c r="S37">
+        <v>14.1</v>
+      </c>
+      <c r="T37" t="s">
+        <v>102</v>
+      </c>
+      <c r="U37">
+        <v>9</v>
+      </c>
+      <c r="V37" t="s">
+        <v>156</v>
+      </c>
+      <c r="W37">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Y37">
+        <f t="shared" si="0"/>
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>226</v>
+      </c>
+      <c r="C38">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D38" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F38" t="s">
+        <v>229</v>
+      </c>
+      <c r="G38">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H38" t="s">
+        <v>173</v>
+      </c>
+      <c r="I38">
+        <v>4.7</v>
+      </c>
+      <c r="J38" t="s">
+        <v>213</v>
+      </c>
+      <c r="K38">
+        <v>10.5</v>
+      </c>
+      <c r="L38" t="s">
+        <v>67</v>
+      </c>
+      <c r="M38">
+        <v>9.9</v>
+      </c>
+      <c r="N38" t="s">
+        <v>154</v>
+      </c>
+      <c r="O38">
+        <v>6.4</v>
+      </c>
+      <c r="P38" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q38">
+        <v>6.2</v>
+      </c>
+      <c r="R38" t="s">
+        <v>40</v>
+      </c>
+      <c r="S38">
+        <v>14.2</v>
+      </c>
+      <c r="T38" t="s">
+        <v>139</v>
+      </c>
+      <c r="U38">
+        <v>8.4</v>
+      </c>
+      <c r="V38" t="s">
+        <v>99</v>
+      </c>
+      <c r="W38">
+        <v>7</v>
+      </c>
+      <c r="Y38">
+        <f t="shared" si="0"/>
+        <v>82.100000000000009</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D39" t="s">
+        <v>90</v>
+      </c>
+      <c r="E39">
+        <v>5.4</v>
+      </c>
+      <c r="F39" t="s">
+        <v>126</v>
+      </c>
+      <c r="G39">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H39" t="s">
+        <v>210</v>
+      </c>
+      <c r="I39">
+        <v>4.3</v>
+      </c>
+      <c r="J39" t="s">
+        <v>51</v>
+      </c>
+      <c r="K39">
+        <v>13.4</v>
+      </c>
+      <c r="L39" t="s">
+        <v>67</v>
+      </c>
+      <c r="M39">
+        <v>10</v>
+      </c>
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39">
+        <v>8.5</v>
+      </c>
+      <c r="P39" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q39">
+        <v>7.5</v>
+      </c>
+      <c r="R39" t="s">
+        <v>106</v>
+      </c>
+      <c r="S39">
+        <v>6.3</v>
+      </c>
+      <c r="T39" t="s">
+        <v>40</v>
+      </c>
+      <c r="U39">
+        <v>14.2</v>
+      </c>
+      <c r="V39" t="s">
+        <v>156</v>
+      </c>
+      <c r="W39">
+        <v>5</v>
+      </c>
+      <c r="Y39">
+        <f t="shared" si="0"/>
+        <v>84.100000000000009</v>
       </c>
     </row>
   </sheetData>
@@ -2742,7 +9816,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B09267FD-053D-459B-8428-907F40AAF5A8}">
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -2759,7 +9833,7 @@
     <col min="22" max="22" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2830,17 +9904,25 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y2">
+        <f t="shared" ref="Y2:Y3" si="0">SUM(C2:W2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2910,8 +9992,12 @@
       <c r="W4">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y4">
+        <f>SUM(C4:W4)</f>
+        <v>83.199999999999989</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2981,8 +10067,12 @@
       <c r="W5">
         <v>5.7</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y5">
+        <f t="shared" ref="Y5:Y39" si="1">SUM(C5:W5)</f>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3052,8 +10142,12 @@
       <c r="W6">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y6">
+        <f t="shared" si="1"/>
+        <v>83.600000000000009</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3123,8 +10217,12 @@
       <c r="W7">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y7">
+        <f t="shared" si="1"/>
+        <v>82.399999999999991</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3194,8 +10292,12 @@
       <c r="W8">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y8">
+        <f t="shared" si="1"/>
+        <v>83.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3265,8 +10367,12 @@
       <c r="W9">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y9">
+        <f t="shared" si="1"/>
+        <v>83.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3336,8 +10442,12 @@
       <c r="W10">
         <v>6.3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y10">
+        <f t="shared" si="1"/>
+        <v>82.999999999999986</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3407,8 +10517,12 @@
       <c r="W11">
         <v>5.7</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y11">
+        <f t="shared" si="1"/>
+        <v>83.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3478,8 +10592,12 @@
       <c r="W12">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y12">
+        <f t="shared" si="1"/>
+        <v>81.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3549,8 +10667,12 @@
       <c r="W13">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y13">
+        <f t="shared" si="1"/>
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3620,8 +10742,12 @@
       <c r="W14">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y14">
+        <f t="shared" si="1"/>
+        <v>83.499999999999986</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3691,8 +10817,12 @@
       <c r="W15">
         <v>7.1</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y15">
+        <f t="shared" si="1"/>
+        <v>83.899999999999991</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3762,8 +10892,12 @@
       <c r="W16">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y16">
+        <f t="shared" si="1"/>
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3833,8 +10967,12 @@
       <c r="W17">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y17">
+        <f t="shared" si="1"/>
+        <v>83.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3904,8 +11042,12 @@
       <c r="W18">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y18">
+        <f t="shared" si="1"/>
+        <v>83.199999999999989</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3975,8 +11117,12 @@
       <c r="W19">
         <v>6.6</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y19">
+        <f t="shared" si="1"/>
+        <v>83.899999999999991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4046,8 +11192,12 @@
       <c r="W20">
         <v>8.8000000000000007</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y20">
+        <f t="shared" si="1"/>
+        <v>83.399999999999977</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4117,8 +11267,12 @@
       <c r="W21">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y21">
+        <f t="shared" si="1"/>
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4188,8 +11342,12 @@
       <c r="W22">
         <v>5.7</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y22">
+        <f t="shared" si="1"/>
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4259,8 +11417,12 @@
       <c r="W23">
         <v>5.7</v>
       </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y23">
+        <f t="shared" si="1"/>
+        <v>83.700000000000017</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4330,8 +11492,12 @@
       <c r="W24">
         <v>7.3</v>
       </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y24">
+        <f t="shared" si="1"/>
+        <v>83.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4401,8 +11567,12 @@
       <c r="W25">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y25">
+        <f t="shared" si="1"/>
+        <v>82.59999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4472,8 +11642,12 @@
       <c r="W26">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y26">
+        <f t="shared" si="1"/>
+        <v>82.399999999999991</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4543,8 +11717,12 @@
       <c r="W27">
         <v>6.3</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y27">
+        <f t="shared" si="1"/>
+        <v>79.600000000000009</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4614,8 +11792,12 @@
       <c r="W28">
         <v>6.4</v>
       </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y28">
+        <f t="shared" si="1"/>
+        <v>83.700000000000017</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4685,8 +11867,12 @@
       <c r="W29">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y29">
+        <f t="shared" si="1"/>
+        <v>83.000000000000014</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4756,8 +11942,12 @@
       <c r="W30">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y30">
+        <f t="shared" si="1"/>
+        <v>77.400000000000006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4827,8 +12017,12 @@
       <c r="W31">
         <v>7.3</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y31">
+        <f t="shared" si="1"/>
+        <v>80.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4898,8 +12092,12 @@
       <c r="W32">
         <v>5.3</v>
       </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y32">
+        <f t="shared" si="1"/>
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4969,8 +12167,12 @@
       <c r="W33">
         <v>7.7</v>
       </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y33">
+        <f t="shared" si="1"/>
+        <v>81.500000000000014</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5040,8 +12242,12 @@
       <c r="W34">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y34">
+        <f t="shared" si="1"/>
+        <v>81.299999999999983</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5111,8 +12317,12 @@
       <c r="W35">
         <v>9.6</v>
       </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y35">
+        <f t="shared" si="1"/>
+        <v>76.599999999999994</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5182,8 +12392,12 @@
       <c r="W36">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y36">
+        <f t="shared" si="1"/>
+        <v>80.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5253,8 +12467,12 @@
       <c r="W37">
         <v>6.7</v>
       </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y37">
+        <f t="shared" si="1"/>
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5324,8 +12542,12 @@
       <c r="W38">
         <v>5.3</v>
       </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="Y38">
+        <f t="shared" si="1"/>
+        <v>81.900000000000006</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5394,6 +12616,10 @@
       </c>
       <c r="W39">
         <v>5.8</v>
+      </c>
+      <c r="Y39">
+        <f t="shared" si="1"/>
+        <v>84.299999999999983</v>
       </c>
     </row>
   </sheetData>

--- a/Scout Selection.xlsx
+++ b/Scout Selection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djrre\OneDrive\Documents\Uni\Year 3\Maths and Data Modelling\Project 3 FPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84459217-9799-43EC-B157-58338578E4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB19B63A-1562-479F-ABBD-71CA2E3E8844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6BE00737-8581-4113-9953-3E2437BA74CB}"/>
+    <workbookView xWindow="22944" yWindow="-1500" windowWidth="23232" windowHeight="13872" xr2:uid="{6BE00737-8581-4113-9953-3E2437BA74CB}"/>
   </bookViews>
   <sheets>
     <sheet name="21.22" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="299">
   <si>
     <t>Gameweek</t>
   </si>
@@ -933,6 +933,9 @@
   </si>
   <si>
     <t>Marcos Alonso</t>
+  </si>
+  <si>
+    <t>Tariq Lamptey</t>
   </si>
 </sst>
 </file>
@@ -1311,23 +1314,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1967FA83-A894-45AF-9397-5DC671B5901D}">
   <dimension ref="A1:Y39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="14" max="14" width="17.6640625" customWidth="1"/>
-    <col min="16" max="16" width="17.6640625" customWidth="1"/>
-    <col min="18" max="18" width="17.6640625" customWidth="1"/>
-    <col min="20" max="20" width="17.6640625" customWidth="1"/>
-    <col min="22" max="22" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.7109375" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" customWidth="1"/>
+    <col min="20" max="20" width="17.7109375" customWidth="1"/>
+    <col min="22" max="22" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1398,7 +1401,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1407,7 +1410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1482,7 +1485,7 @@
         <v>83.499999999999986</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1557,7 +1560,7 @@
         <v>82.800000000000011</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1632,7 +1635,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1707,7 +1710,7 @@
         <v>83.300000000000011</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1782,7 +1785,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1857,7 +1860,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1932,7 +1935,7 @@
         <v>83.499999999999986</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2007,7 +2010,7 @@
         <v>83.499999999999986</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2082,7 +2085,7 @@
         <v>83.600000000000009</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2157,7 +2160,7 @@
         <v>83.199999999999989</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2232,7 +2235,7 @@
         <v>83.7</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2307,7 +2310,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2382,7 +2385,7 @@
         <v>83.7</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2457,7 +2460,7 @@
         <v>83.7</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2532,25 +2535,157 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F18" t="s">
+        <v>202</v>
+      </c>
+      <c r="G18">
+        <v>5.3</v>
+      </c>
+      <c r="H18" t="s">
+        <v>298</v>
+      </c>
+      <c r="I18">
+        <v>4.5</v>
+      </c>
+      <c r="J18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18">
+        <v>13.1</v>
+      </c>
+      <c r="L18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18">
+        <v>8</v>
+      </c>
+      <c r="N18" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18">
+        <v>8</v>
+      </c>
+      <c r="P18" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q18">
+        <v>7.6</v>
+      </c>
+      <c r="R18" t="s">
+        <v>52</v>
+      </c>
+      <c r="S18">
+        <v>10.6</v>
+      </c>
+      <c r="T18" t="s">
+        <v>282</v>
+      </c>
+      <c r="U18">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="V18" t="s">
+        <v>259</v>
+      </c>
+      <c r="W18">
+        <v>5.8</v>
+      </c>
       <c r="Y18">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+        <v>83.999999999999986</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>5.5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19">
+        <v>6.8</v>
+      </c>
+      <c r="H19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19">
+        <v>6.3</v>
+      </c>
+      <c r="J19" t="s">
+        <v>196</v>
+      </c>
+      <c r="K19">
+        <v>5</v>
+      </c>
+      <c r="L19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19">
+        <v>13.1</v>
+      </c>
+      <c r="N19" t="s">
+        <v>52</v>
+      </c>
+      <c r="O19">
+        <v>10.6</v>
+      </c>
+      <c r="P19" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q19">
+        <v>8</v>
+      </c>
+      <c r="R19" t="s">
+        <v>76</v>
+      </c>
+      <c r="S19">
+        <v>6.6</v>
+      </c>
+      <c r="T19" t="s">
+        <v>129</v>
+      </c>
+      <c r="U19">
+        <v>6</v>
+      </c>
+      <c r="V19" t="s">
+        <v>102</v>
+      </c>
+      <c r="W19">
+        <v>7.7</v>
+      </c>
       <c r="Y19">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2625,7 +2760,7 @@
         <v>82.500000000000014</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2700,7 +2835,7 @@
         <v>84.000000000000014</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2775,7 +2910,7 @@
         <v>80.5</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2850,7 +2985,7 @@
         <v>84.5</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2925,7 +3060,7 @@
         <v>81.900000000000006</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3000,7 +3135,7 @@
         <v>83.600000000000009</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3075,7 +3210,7 @@
         <v>84.3</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3150,16 +3285,76 @@
         <v>83.7</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28">
+        <v>5.4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>261</v>
+      </c>
+      <c r="E28">
+        <v>5.8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+      <c r="H28" t="s">
+        <v>288</v>
+      </c>
+      <c r="I28">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="J28" t="s">
+        <v>82</v>
+      </c>
+      <c r="K28">
+        <v>11.9</v>
+      </c>
+      <c r="L28" t="s">
+        <v>66</v>
+      </c>
+      <c r="M28">
+        <v>11.7</v>
+      </c>
+      <c r="N28" t="s">
+        <v>75</v>
+      </c>
+      <c r="O28">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="R28" t="s">
+        <v>31</v>
+      </c>
+      <c r="S28">
+        <v>12.2</v>
+      </c>
+      <c r="T28" t="s">
+        <v>292</v>
+      </c>
+      <c r="U28">
+        <v>6.5</v>
+      </c>
+      <c r="V28" t="s">
+        <v>275</v>
+      </c>
+      <c r="W28">
+        <v>5.5</v>
+      </c>
       <c r="Y28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+        <v>77.100000000000009</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3234,7 +3429,7 @@
         <v>80.7</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3309,7 +3504,7 @@
         <v>83.999999999999986</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3384,7 +3579,7 @@
         <v>79.600000000000009</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3452,14 +3647,14 @@
         <v>292</v>
       </c>
       <c r="W32">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y32">
         <f t="shared" si="0"/>
-        <v>82.300000000000011</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+        <v>83.300000000000011</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3534,7 +3729,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3609,7 +3804,7 @@
         <v>83.9</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3684,7 +3879,7 @@
         <v>83.7</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3759,7 +3954,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3834,7 +4029,7 @@
         <v>83.8</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3909,13 +4104,79 @@
         <v>83.399999999999991</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
+      <c r="B39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39">
+        <v>4.3</v>
+      </c>
+      <c r="D39" t="s">
+        <v>243</v>
+      </c>
+      <c r="E39">
+        <v>7.3</v>
+      </c>
+      <c r="F39" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39">
+        <v>6.4</v>
+      </c>
+      <c r="H39" t="s">
+        <v>202</v>
+      </c>
+      <c r="I39">
+        <v>5.3</v>
+      </c>
+      <c r="J39" t="s">
+        <v>176</v>
+      </c>
+      <c r="K39">
+        <v>4.3</v>
+      </c>
+      <c r="L39" t="s">
+        <v>82</v>
+      </c>
+      <c r="M39">
+        <v>12.1</v>
+      </c>
+      <c r="N39" t="s">
+        <v>67</v>
+      </c>
+      <c r="O39">
+        <v>11.2</v>
+      </c>
+      <c r="P39" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q39">
+        <v>8.1</v>
+      </c>
+      <c r="R39" t="s">
+        <v>45</v>
+      </c>
+      <c r="S39">
+        <v>7.7</v>
+      </c>
+      <c r="T39" t="s">
+        <v>145</v>
+      </c>
+      <c r="U39">
+        <v>10.3</v>
+      </c>
+      <c r="V39" t="s">
+        <v>80</v>
+      </c>
+      <c r="W39">
+        <v>6.8</v>
+      </c>
       <c r="Y39">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>83.8</v>
       </c>
     </row>
   </sheetData>
@@ -3927,23 +4188,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6523D19C-AF7E-47F2-B7FC-038031819EDE}">
   <dimension ref="A1:Y39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="14" max="14" width="17.6640625" customWidth="1"/>
-    <col min="16" max="16" width="17.6640625" customWidth="1"/>
-    <col min="18" max="18" width="17.6640625" customWidth="1"/>
-    <col min="20" max="20" width="17.6640625" customWidth="1"/>
-    <col min="22" max="22" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.7109375" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" customWidth="1"/>
+    <col min="20" max="20" width="17.7109375" customWidth="1"/>
+    <col min="22" max="22" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4014,7 +4275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4089,7 +4350,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4164,7 +4425,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4239,7 +4500,7 @@
         <v>82.9</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4314,7 +4575,7 @@
         <v>82.800000000000011</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4389,7 +4650,7 @@
         <v>83.200000000000017</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4464,7 +4725,7 @@
         <v>83.40000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4539,7 +4800,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4614,7 +4875,7 @@
         <v>82.9</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4689,7 +4950,7 @@
         <v>83.499999999999986</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4764,7 +5025,7 @@
         <v>84.200000000000017</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4839,7 +5100,7 @@
         <v>83.7</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4914,7 +5175,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4989,7 +5250,7 @@
         <v>83.8</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5064,7 +5325,7 @@
         <v>81.7</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5139,7 +5400,7 @@
         <v>82.3</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5214,7 +5475,7 @@
         <v>84.399999999999991</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5289,7 +5550,7 @@
         <v>83.8</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5364,7 +5625,7 @@
         <v>84.399999999999991</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5439,7 +5700,7 @@
         <v>84.699999999999989</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5514,7 +5775,7 @@
         <v>84.199999999999989</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5589,7 +5850,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5664,7 +5925,7 @@
         <v>74.7</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5739,7 +6000,7 @@
         <v>77.100000000000009</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5814,7 +6075,7 @@
         <v>80.799999999999983</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5889,7 +6150,7 @@
         <v>82.999999999999986</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5964,7 +6225,7 @@
         <v>80.099999999999994</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6039,7 +6300,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6114,7 +6375,7 @@
         <v>76.900000000000006</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6189,7 +6450,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6264,7 +6525,7 @@
         <v>83.399999999999991</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6339,7 +6600,7 @@
         <v>83.100000000000009</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6414,7 +6675,7 @@
         <v>79.7</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6489,7 +6750,7 @@
         <v>83.4</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6564,7 +6825,7 @@
         <v>82.600000000000009</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6639,7 +6900,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6714,7 +6975,7 @@
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6789,7 +7050,7 @@
         <v>84.1</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6872,23 +7133,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2177F9E4-D044-4408-B3F2-34055E8639B0}">
   <dimension ref="A1:Y39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="14" max="14" width="17.6640625" customWidth="1"/>
-    <col min="16" max="16" width="17.6640625" customWidth="1"/>
-    <col min="18" max="18" width="17.6640625" customWidth="1"/>
-    <col min="20" max="20" width="17.6640625" customWidth="1"/>
-    <col min="22" max="22" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.7109375" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" customWidth="1"/>
+    <col min="20" max="20" width="17.7109375" customWidth="1"/>
+    <col min="22" max="22" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6959,7 +7220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7034,7 +7295,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7109,7 +7370,7 @@
         <v>83.2</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7184,7 +7445,7 @@
         <v>79.3</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7259,7 +7520,7 @@
         <v>81.699999999999989</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -7334,7 +7595,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -7409,7 +7670,7 @@
         <v>83.600000000000009</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7484,7 +7745,7 @@
         <v>82.899999999999991</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7559,7 +7820,7 @@
         <v>83.899999999999991</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -7634,7 +7895,7 @@
         <v>83.8</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -7709,7 +7970,7 @@
         <v>83.199999999999989</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -7784,7 +8045,7 @@
         <v>83.399999999999991</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -7859,7 +8120,7 @@
         <v>84.2</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -7934,7 +8195,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -8009,7 +8270,7 @@
         <v>83.299999999999983</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -8084,7 +8345,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -8159,7 +8420,7 @@
         <v>84.000000000000014</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -8234,7 +8495,7 @@
         <v>83.399999999999991</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -8309,7 +8570,7 @@
         <v>82.100000000000009</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -8384,7 +8645,7 @@
         <v>83.9</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -8459,7 +8720,7 @@
         <v>84.1</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -8534,7 +8795,7 @@
         <v>72.600000000000009</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -8609,7 +8870,7 @@
         <v>79.8</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -8684,7 +8945,7 @@
         <v>84.6</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -8759,7 +9020,7 @@
         <v>84.699999999999989</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -8834,7 +9095,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -8909,7 +9170,7 @@
         <v>82.8</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -8984,7 +9245,7 @@
         <v>84.200000000000017</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -9059,7 +9320,7 @@
         <v>73.5</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -9134,7 +9395,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -9209,7 +9470,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -9284,7 +9545,7 @@
         <v>84.4</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -9359,7 +9620,7 @@
         <v>84.6</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -9434,7 +9695,7 @@
         <v>84.2</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -9509,7 +9770,7 @@
         <v>76.600000000000009</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -9584,7 +9845,7 @@
         <v>70.199999999999989</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9659,7 +9920,7 @@
         <v>82.8</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -9734,7 +9995,7 @@
         <v>82.100000000000009</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9817,23 +10078,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B09267FD-053D-459B-8428-907F40AAF5A8}">
   <dimension ref="A1:Y39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="14" max="14" width="17.6640625" customWidth="1"/>
-    <col min="16" max="16" width="17.6640625" customWidth="1"/>
-    <col min="18" max="18" width="17.6640625" customWidth="1"/>
-    <col min="20" max="20" width="17.6640625" customWidth="1"/>
-    <col min="22" max="22" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.7109375" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" customWidth="1"/>
+    <col min="20" max="20" width="17.7109375" customWidth="1"/>
+    <col min="22" max="22" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9904,7 +10165,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -9913,7 +10174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -9922,7 +10183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -9997,7 +10258,7 @@
         <v>83.199999999999989</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -10072,7 +10333,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -10147,7 +10408,7 @@
         <v>83.600000000000009</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -10222,7 +10483,7 @@
         <v>82.399999999999991</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -10297,7 +10558,7 @@
         <v>83.3</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -10372,7 +10633,7 @@
         <v>83.3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -10447,7 +10708,7 @@
         <v>82.999999999999986</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -10522,7 +10783,7 @@
         <v>83.4</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -10597,7 +10858,7 @@
         <v>81.5</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -10672,7 +10933,7 @@
         <v>83.7</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -10747,7 +11008,7 @@
         <v>83.499999999999986</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -10822,7 +11083,7 @@
         <v>83.899999999999991</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -10897,7 +11158,7 @@
         <v>83.8</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -10972,7 +11233,7 @@
         <v>83.3</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -11047,7 +11308,7 @@
         <v>83.199999999999989</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -11122,7 +11383,7 @@
         <v>83.899999999999991</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -11197,7 +11458,7 @@
         <v>83.399999999999977</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -11272,7 +11533,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -11347,7 +11608,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -11422,7 +11683,7 @@
         <v>83.700000000000017</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -11497,7 +11758,7 @@
         <v>83.1</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -11572,7 +11833,7 @@
         <v>82.59999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -11647,7 +11908,7 @@
         <v>82.399999999999991</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -11722,7 +11983,7 @@
         <v>79.600000000000009</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -11797,7 +12058,7 @@
         <v>83.700000000000017</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -11872,7 +12133,7 @@
         <v>83.000000000000014</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -11947,7 +12208,7 @@
         <v>77.400000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -12022,7 +12283,7 @@
         <v>80.8</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -12097,7 +12358,7 @@
         <v>81.3</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -12172,7 +12433,7 @@
         <v>81.500000000000014</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -12247,7 +12508,7 @@
         <v>81.299999999999983</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -12322,7 +12583,7 @@
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -12397,7 +12658,7 @@
         <v>80.3</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -12472,7 +12733,7 @@
         <v>79.2</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -12547,7 +12808,7 @@
         <v>81.900000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
